--- a/Assets/@Resources/Data/Excel/CreatureData.xlsx
+++ b/Assets/@Resources/Data/Excel/CreatureData.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CreatureData" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreatureData" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,32 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EBF3FA"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -65,17 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,222 +413,419 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>DataId</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PrefabLabel</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>IconLabel</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>MaxHp</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Atk</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>PhysicalAtk</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>Def</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>MoveSpeed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>TotalExp</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>RewardGold</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>DropItemId</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>DropCount</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>DropChance</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>MagicAtk</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>CritRate</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>CritDamage</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>AtkSpeed</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>PhysicalResist</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>MagicResist</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Evasion</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>RecoveryRate</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>UniqueSkillName</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>UniqueSkillDesc</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>AttackSfx</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>OnHitSfx</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>DieSfx</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>AnimController</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Habitat</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>DmgAmp</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Rarity</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>MonsterAttackDelay</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>EncounterRate</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>InterestRate</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>MaxKillCount</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>SpawnY</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>DamageFontYOffset</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>데이터ID</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>이름</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>프리팹명</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>아이콘명</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>이름(로컬키)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>프리팹</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>아이콘</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>최대HP</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>공격력</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>방어력</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>이동속도</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>제공경험치</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>제공골드</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>드롭아이템ID</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>드롭수량</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>드롭확률(0~1)</t>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>물공</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>방어</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>이속</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>경험치</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>골드</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>드랍ID</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>드랍수</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>드랍확률0~1</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>마공</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>치명%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>치명피해%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>명중%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>공속%</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>물저%</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>마저%</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>회피%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>회복%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>고유기술명(로컬키)</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>고유기술설명(로컬키)</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>공격SFX</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>피격SFX</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>사망SFX</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>애니컨트롤러</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>서식지(로컬키)</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>피해증폭%</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>희귀도</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>공격대기(초)</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>조우확률0~1</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>관심확률0~1</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>최대킬카운트</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>스폰Y</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>데미지폰트Y</t>
         </is>
       </c>
     </row>
@@ -666,26 +835,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>젤리 퐁</t>
+          <t>SlimeNameText</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Slime</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Slime_Idle_4</t>
+        </is>
+      </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -694,13 +867,85 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>1001</v>
+        <v>10001</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>80</v>
+      </c>
+      <c r="R4" t="n">
+        <v>100</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>BreezingWindForestNameText</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -709,26 +954,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>라비 슬라임</t>
+          <t>RabiSlimeNameText</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RabiSlime</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>slime_monster_0</t>
+        </is>
+      </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="F5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G5" t="n">
         <v>7</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>15</v>
@@ -737,13 +986,204 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>1002</v>
+        <v>10002</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>80</v>
+      </c>
+      <c r="R5" t="n">
+        <v>100</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GoblinNameText</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>goblin_monster_0</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>130</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>15</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10001</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>80</v>
+      </c>
+      <c r="R6" t="n">
+        <v>100</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Goblin</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>BreezingWindForestNameText</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/@Resources/Data/Excel/CreatureData.xlsx
+++ b/Assets/@Resources/Data/Excel/CreatureData.xlsx
@@ -17360,7 +17360,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>Mon_2220</t>
+          <t>Mon_BreezingWindForest_0</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -17495,7 +17495,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>Mon_2221</t>
+          <t>Mon_BreezingWindForest_1</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -17630,7 +17630,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>Mon_2222</t>
+          <t>Mon_BreezingWindForest_2</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>Mon_2223</t>
+          <t>Mon_BreezingWindForest_3</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>Mon_2224</t>
+          <t>Mon_BreezingWindForest_4</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>Mon_2225</t>
+          <t>Mon_BreezingWindForest_5</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
@@ -18170,7 +18170,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>Mon_2226</t>
+          <t>Mon_BreezingWindForest_6</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -18305,7 +18305,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>Mon_2227</t>
+          <t>Mon_BreezingWindForest_7</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -18440,7 +18440,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>Mon_2228</t>
+          <t>Mon_BreezingWindForest_8</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>Mon_2229</t>
+          <t>Mon_BreezingWindForest_9</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -18710,7 +18710,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>Mon_2230</t>
+          <t>Mon_BreezingWindForest_0</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>Mon_2231</t>
+          <t>Mon_BreezingWindForest_1</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>Mon_2232</t>
+          <t>Mon_BreezingWindForest_2</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -19115,7 +19115,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>Mon_2233</t>
+          <t>Mon_BreezingWindForest_3</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>Mon_2234</t>
+          <t>Mon_BreezingWindForest_4</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
@@ -19385,7 +19385,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>Mon_2235</t>
+          <t>Mon_BreezingWindForest_5</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>Mon_2236</t>
+          <t>Mon_BreezingWindForest_6</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">

--- a/Assets/@Resources/Data/Excel/CreatureData.xlsx
+++ b/Assets/@Resources/Data/Excel/CreatureData.xlsx
@@ -913,7 +913,7 @@
         <v>1</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI4" t="n">
         <v>100</v>
@@ -1048,7 +1048,7 @@
         <v>0.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI5" t="n">
         <v>100</v>
@@ -1183,7 +1183,7 @@
         <v>0.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI6" t="n">
         <v>100</v>
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI7" t="n">
         <v>100</v>
@@ -1453,7 +1453,7 @@
         <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI8" t="n">
         <v>100</v>
@@ -1588,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI9" t="n">
         <v>100</v>
@@ -1723,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI10" t="n">
         <v>100</v>
@@ -1858,7 +1858,7 @@
         <v>0.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI11" t="n">
         <v>100</v>
@@ -1993,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI12" t="n">
         <v>100</v>
@@ -2128,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI13" t="n">
         <v>100</v>
@@ -2263,7 +2263,7 @@
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI14" t="n">
         <v>100</v>
@@ -2398,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI15" t="n">
         <v>100</v>
@@ -2533,7 +2533,7 @@
         <v>0.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI16" t="n">
         <v>100</v>
@@ -2668,7 +2668,7 @@
         <v>1</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI17" t="n">
         <v>100</v>
@@ -2803,7 +2803,7 @@
         <v>1</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI18" t="n">
         <v>100</v>
@@ -2938,7 +2938,7 @@
         <v>1</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI19" t="n">
         <v>100</v>
@@ -3073,7 +3073,7 @@
         <v>1</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI20" t="n">
         <v>100</v>
@@ -3208,7 +3208,7 @@
         <v>0.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI21" t="n">
         <v>100</v>
@@ -3343,7 +3343,7 @@
         <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI22" t="n">
         <v>100</v>
@@ -3478,7 +3478,7 @@
         <v>0.08</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI23" t="n">
         <v>100</v>
@@ -3613,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI24" t="n">
         <v>100</v>
@@ -3748,7 +3748,7 @@
         <v>1</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI25" t="n">
         <v>100</v>
@@ -3883,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI26" t="n">
         <v>100</v>
@@ -4018,7 +4018,7 @@
         <v>1</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI27" t="n">
         <v>100</v>
@@ -4153,7 +4153,7 @@
         <v>0.4</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI28" t="n">
         <v>100</v>
@@ -4288,7 +4288,7 @@
         <v>1</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI29" t="n">
         <v>100</v>
@@ -4423,7 +4423,7 @@
         <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI30" t="n">
         <v>100</v>
@@ -4558,7 +4558,7 @@
         <v>1</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI31" t="n">
         <v>100</v>
@@ -4693,7 +4693,7 @@
         <v>1</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI32" t="n">
         <v>100</v>
@@ -4828,7 +4828,7 @@
         <v>0.4</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI33" t="n">
         <v>100</v>
@@ -4963,7 +4963,7 @@
         <v>1</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI34" t="n">
         <v>100</v>
@@ -5098,7 +5098,7 @@
         <v>1</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI35" t="n">
         <v>100</v>
@@ -5233,7 +5233,7 @@
         <v>1</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI36" t="n">
         <v>100</v>
@@ -5368,7 +5368,7 @@
         <v>1</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI37" t="n">
         <v>100</v>
@@ -5503,7 +5503,7 @@
         <v>0.4</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI38" t="n">
         <v>100</v>
@@ -5638,7 +5638,7 @@
         <v>1</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI39" t="n">
         <v>100</v>
@@ -5773,7 +5773,7 @@
         <v>0.08</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI40" t="n">
         <v>100</v>
@@ -5908,7 +5908,7 @@
         <v>1</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI41" t="n">
         <v>100</v>
@@ -6043,7 +6043,7 @@
         <v>1</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI42" t="n">
         <v>100</v>
@@ -6178,7 +6178,7 @@
         <v>1</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI43" t="n">
         <v>100</v>
@@ -6313,7 +6313,7 @@
         <v>1</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI44" t="n">
         <v>100</v>
@@ -6448,7 +6448,7 @@
         <v>0.4</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI45" t="n">
         <v>100</v>
@@ -6583,7 +6583,7 @@
         <v>1</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI46" t="n">
         <v>100</v>
@@ -6718,7 +6718,7 @@
         <v>1</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI47" t="n">
         <v>100</v>
@@ -6853,7 +6853,7 @@
         <v>1</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI48" t="n">
         <v>100</v>
@@ -6988,7 +6988,7 @@
         <v>1</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI49" t="n">
         <v>100</v>
@@ -7123,7 +7123,7 @@
         <v>0.4</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI50" t="n">
         <v>100</v>
@@ -7258,7 +7258,7 @@
         <v>1</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI51" t="n">
         <v>100</v>
@@ -7393,7 +7393,7 @@
         <v>1</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI52" t="n">
         <v>100</v>
@@ -7528,7 +7528,7 @@
         <v>1</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI53" t="n">
         <v>100</v>
@@ -7663,7 +7663,7 @@
         <v>1</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI54" t="n">
         <v>100</v>
@@ -7798,7 +7798,7 @@
         <v>0.4</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI55" t="n">
         <v>100</v>
@@ -7933,7 +7933,7 @@
         <v>1</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI56" t="n">
         <v>100</v>
@@ -8068,7 +8068,7 @@
         <v>0.08</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI57" t="n">
         <v>100</v>
@@ -8203,7 +8203,7 @@
         <v>1</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI58" t="n">
         <v>100</v>
@@ -8338,7 +8338,7 @@
         <v>1</v>
       </c>
       <c r="AH59" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI59" t="n">
         <v>100</v>
@@ -8473,7 +8473,7 @@
         <v>1</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI60" t="n">
         <v>100</v>
@@ -8608,7 +8608,7 @@
         <v>1</v>
       </c>
       <c r="AH61" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI61" t="n">
         <v>100</v>
@@ -8743,7 +8743,7 @@
         <v>0.4</v>
       </c>
       <c r="AH62" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI62" t="n">
         <v>100</v>
@@ -8878,7 +8878,7 @@
         <v>1</v>
       </c>
       <c r="AH63" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI63" t="n">
         <v>100</v>
@@ -9013,7 +9013,7 @@
         <v>1</v>
       </c>
       <c r="AH64" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI64" t="n">
         <v>100</v>
@@ -9148,7 +9148,7 @@
         <v>1</v>
       </c>
       <c r="AH65" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI65" t="n">
         <v>100</v>
@@ -9283,7 +9283,7 @@
         <v>1</v>
       </c>
       <c r="AH66" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI66" t="n">
         <v>100</v>
@@ -9418,7 +9418,7 @@
         <v>0.4</v>
       </c>
       <c r="AH67" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI67" t="n">
         <v>100</v>
@@ -9553,7 +9553,7 @@
         <v>1</v>
       </c>
       <c r="AH68" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI68" t="n">
         <v>100</v>
@@ -9688,7 +9688,7 @@
         <v>1</v>
       </c>
       <c r="AH69" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI69" t="n">
         <v>100</v>
@@ -9823,7 +9823,7 @@
         <v>1</v>
       </c>
       <c r="AH70" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI70" t="n">
         <v>100</v>
@@ -9958,7 +9958,7 @@
         <v>1</v>
       </c>
       <c r="AH71" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI71" t="n">
         <v>100</v>
@@ -10093,7 +10093,7 @@
         <v>0.4</v>
       </c>
       <c r="AH72" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI72" t="n">
         <v>100</v>
@@ -10228,7 +10228,7 @@
         <v>1</v>
       </c>
       <c r="AH73" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI73" t="n">
         <v>100</v>
@@ -10363,7 +10363,7 @@
         <v>0.08</v>
       </c>
       <c r="AH74" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI74" t="n">
         <v>100</v>
@@ -10498,7 +10498,7 @@
         <v>1</v>
       </c>
       <c r="AH75" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI75" t="n">
         <v>100</v>
@@ -10633,7 +10633,7 @@
         <v>1</v>
       </c>
       <c r="AH76" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI76" t="n">
         <v>100</v>
@@ -10768,7 +10768,7 @@
         <v>1</v>
       </c>
       <c r="AH77" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI77" t="n">
         <v>100</v>
@@ -10903,7 +10903,7 @@
         <v>1</v>
       </c>
       <c r="AH78" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI78" t="n">
         <v>100</v>
@@ -11038,7 +11038,7 @@
         <v>0.4</v>
       </c>
       <c r="AH79" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI79" t="n">
         <v>100</v>
@@ -11173,7 +11173,7 @@
         <v>1</v>
       </c>
       <c r="AH80" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI80" t="n">
         <v>100</v>
@@ -11308,7 +11308,7 @@
         <v>1</v>
       </c>
       <c r="AH81" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI81" t="n">
         <v>100</v>
@@ -11443,7 +11443,7 @@
         <v>1</v>
       </c>
       <c r="AH82" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI82" t="n">
         <v>100</v>
@@ -11578,7 +11578,7 @@
         <v>1</v>
       </c>
       <c r="AH83" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI83" t="n">
         <v>100</v>
@@ -11713,7 +11713,7 @@
         <v>0.4</v>
       </c>
       <c r="AH84" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI84" t="n">
         <v>100</v>
@@ -11848,7 +11848,7 @@
         <v>1</v>
       </c>
       <c r="AH85" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI85" t="n">
         <v>100</v>
@@ -11983,7 +11983,7 @@
         <v>1</v>
       </c>
       <c r="AH86" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI86" t="n">
         <v>100</v>
@@ -12118,7 +12118,7 @@
         <v>1</v>
       </c>
       <c r="AH87" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI87" t="n">
         <v>100</v>
@@ -12253,7 +12253,7 @@
         <v>1</v>
       </c>
       <c r="AH88" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI88" t="n">
         <v>100</v>
@@ -12388,7 +12388,7 @@
         <v>0.4</v>
       </c>
       <c r="AH89" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI89" t="n">
         <v>100</v>
@@ -12523,7 +12523,7 @@
         <v>1</v>
       </c>
       <c r="AH90" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI90" t="n">
         <v>100</v>
@@ -12658,7 +12658,7 @@
         <v>0.08</v>
       </c>
       <c r="AH91" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI91" t="n">
         <v>100</v>
@@ -12793,7 +12793,7 @@
         <v>1</v>
       </c>
       <c r="AH92" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI92" t="n">
         <v>100</v>
@@ -12928,7 +12928,7 @@
         <v>1</v>
       </c>
       <c r="AH93" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI93" t="n">
         <v>100</v>
@@ -13063,7 +13063,7 @@
         <v>1</v>
       </c>
       <c r="AH94" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI94" t="n">
         <v>100</v>
@@ -13198,7 +13198,7 @@
         <v>1</v>
       </c>
       <c r="AH95" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI95" t="n">
         <v>100</v>
@@ -13333,7 +13333,7 @@
         <v>0.4</v>
       </c>
       <c r="AH96" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI96" t="n">
         <v>100</v>
@@ -13468,7 +13468,7 @@
         <v>1</v>
       </c>
       <c r="AH97" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI97" t="n">
         <v>100</v>
@@ -13603,7 +13603,7 @@
         <v>1</v>
       </c>
       <c r="AH98" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI98" t="n">
         <v>100</v>
@@ -13738,7 +13738,7 @@
         <v>1</v>
       </c>
       <c r="AH99" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI99" t="n">
         <v>100</v>
@@ -13873,7 +13873,7 @@
         <v>1</v>
       </c>
       <c r="AH100" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI100" t="n">
         <v>100</v>
@@ -14008,7 +14008,7 @@
         <v>0.4</v>
       </c>
       <c r="AH101" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI101" t="n">
         <v>100</v>
@@ -14143,7 +14143,7 @@
         <v>1</v>
       </c>
       <c r="AH102" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI102" t="n">
         <v>100</v>
@@ -14278,7 +14278,7 @@
         <v>1</v>
       </c>
       <c r="AH103" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI103" t="n">
         <v>100</v>
@@ -14413,7 +14413,7 @@
         <v>1</v>
       </c>
       <c r="AH104" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI104" t="n">
         <v>100</v>
@@ -14548,7 +14548,7 @@
         <v>1</v>
       </c>
       <c r="AH105" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI105" t="n">
         <v>100</v>
@@ -14683,7 +14683,7 @@
         <v>0.4</v>
       </c>
       <c r="AH106" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI106" t="n">
         <v>100</v>
@@ -14818,7 +14818,7 @@
         <v>1</v>
       </c>
       <c r="AH107" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI107" t="n">
         <v>100</v>
@@ -14953,7 +14953,7 @@
         <v>0.08</v>
       </c>
       <c r="AH108" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI108" t="n">
         <v>100</v>
@@ -15088,7 +15088,7 @@
         <v>1</v>
       </c>
       <c r="AH109" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI109" t="n">
         <v>100</v>
@@ -15223,7 +15223,7 @@
         <v>1</v>
       </c>
       <c r="AH110" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI110" t="n">
         <v>100</v>
@@ -15358,7 +15358,7 @@
         <v>1</v>
       </c>
       <c r="AH111" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI111" t="n">
         <v>100</v>
@@ -15493,7 +15493,7 @@
         <v>1</v>
       </c>
       <c r="AH112" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI112" t="n">
         <v>100</v>
@@ -15628,7 +15628,7 @@
         <v>0.4</v>
       </c>
       <c r="AH113" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI113" t="n">
         <v>100</v>
@@ -15763,7 +15763,7 @@
         <v>1</v>
       </c>
       <c r="AH114" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI114" t="n">
         <v>100</v>
@@ -15898,7 +15898,7 @@
         <v>1</v>
       </c>
       <c r="AH115" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI115" t="n">
         <v>100</v>
@@ -16033,7 +16033,7 @@
         <v>1</v>
       </c>
       <c r="AH116" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI116" t="n">
         <v>100</v>
@@ -16168,7 +16168,7 @@
         <v>1</v>
       </c>
       <c r="AH117" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI117" t="n">
         <v>100</v>
@@ -16303,7 +16303,7 @@
         <v>0.4</v>
       </c>
       <c r="AH118" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI118" t="n">
         <v>100</v>
@@ -16438,7 +16438,7 @@
         <v>1</v>
       </c>
       <c r="AH119" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI119" t="n">
         <v>100</v>
@@ -16573,7 +16573,7 @@
         <v>1</v>
       </c>
       <c r="AH120" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI120" t="n">
         <v>100</v>
@@ -16708,7 +16708,7 @@
         <v>1</v>
       </c>
       <c r="AH121" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI121" t="n">
         <v>100</v>
@@ -16843,7 +16843,7 @@
         <v>1</v>
       </c>
       <c r="AH122" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI122" t="n">
         <v>100</v>
@@ -16978,7 +16978,7 @@
         <v>0.4</v>
       </c>
       <c r="AH123" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI123" t="n">
         <v>100</v>
@@ -17113,7 +17113,7 @@
         <v>1</v>
       </c>
       <c r="AH124" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI124" t="n">
         <v>100</v>
@@ -17248,7 +17248,7 @@
         <v>0.08</v>
       </c>
       <c r="AH125" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI125" t="n">
         <v>100</v>
@@ -17383,7 +17383,7 @@
         <v>1</v>
       </c>
       <c r="AH126" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI126" t="n">
         <v>100</v>
@@ -17518,7 +17518,7 @@
         <v>1</v>
       </c>
       <c r="AH127" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI127" t="n">
         <v>100</v>
@@ -17653,7 +17653,7 @@
         <v>1</v>
       </c>
       <c r="AH128" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI128" t="n">
         <v>100</v>
@@ -17788,7 +17788,7 @@
         <v>1</v>
       </c>
       <c r="AH129" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI129" t="n">
         <v>100</v>
@@ -17923,7 +17923,7 @@
         <v>0.4</v>
       </c>
       <c r="AH130" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI130" t="n">
         <v>100</v>
@@ -18058,7 +18058,7 @@
         <v>1</v>
       </c>
       <c r="AH131" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI131" t="n">
         <v>100</v>
@@ -18193,7 +18193,7 @@
         <v>1</v>
       </c>
       <c r="AH132" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI132" t="n">
         <v>100</v>
@@ -18328,7 +18328,7 @@
         <v>1</v>
       </c>
       <c r="AH133" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI133" t="n">
         <v>100</v>
@@ -18463,7 +18463,7 @@
         <v>1</v>
       </c>
       <c r="AH134" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI134" t="n">
         <v>100</v>
@@ -18598,7 +18598,7 @@
         <v>0.4</v>
       </c>
       <c r="AH135" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI135" t="n">
         <v>100</v>
@@ -18733,7 +18733,7 @@
         <v>1</v>
       </c>
       <c r="AH136" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI136" t="n">
         <v>100</v>
@@ -18868,7 +18868,7 @@
         <v>1</v>
       </c>
       <c r="AH137" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI137" t="n">
         <v>100</v>
@@ -19003,7 +19003,7 @@
         <v>1</v>
       </c>
       <c r="AH138" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI138" t="n">
         <v>100</v>
@@ -19138,7 +19138,7 @@
         <v>1</v>
       </c>
       <c r="AH139" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI139" t="n">
         <v>100</v>
@@ -19273,7 +19273,7 @@
         <v>0.4</v>
       </c>
       <c r="AH140" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI140" t="n">
         <v>100</v>
@@ -19408,7 +19408,7 @@
         <v>1</v>
       </c>
       <c r="AH141" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI141" t="n">
         <v>100</v>
@@ -19543,7 +19543,7 @@
         <v>0.08</v>
       </c>
       <c r="AH142" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI142" t="n">
         <v>100</v>
@@ -19678,7 +19678,7 @@
         <v>1</v>
       </c>
       <c r="AH143" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI143" t="n">
         <v>100</v>
@@ -19813,7 +19813,7 @@
         <v>1</v>
       </c>
       <c r="AH144" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI144" t="n">
         <v>100</v>
@@ -19948,7 +19948,7 @@
         <v>1</v>
       </c>
       <c r="AH145" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI145" t="n">
         <v>100</v>
@@ -20083,7 +20083,7 @@
         <v>1</v>
       </c>
       <c r="AH146" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI146" t="n">
         <v>100</v>
@@ -20218,7 +20218,7 @@
         <v>0.4</v>
       </c>
       <c r="AH147" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI147" t="n">
         <v>100</v>
@@ -20353,7 +20353,7 @@
         <v>1</v>
       </c>
       <c r="AH148" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI148" t="n">
         <v>100</v>
@@ -20488,7 +20488,7 @@
         <v>1</v>
       </c>
       <c r="AH149" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI149" t="n">
         <v>100</v>
@@ -20623,7 +20623,7 @@
         <v>1</v>
       </c>
       <c r="AH150" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI150" t="n">
         <v>100</v>
@@ -20758,7 +20758,7 @@
         <v>1</v>
       </c>
       <c r="AH151" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI151" t="n">
         <v>100</v>
@@ -20893,7 +20893,7 @@
         <v>0.4</v>
       </c>
       <c r="AH152" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI152" t="n">
         <v>100</v>
@@ -21028,7 +21028,7 @@
         <v>1</v>
       </c>
       <c r="AH153" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI153" t="n">
         <v>100</v>
@@ -21163,7 +21163,7 @@
         <v>1</v>
       </c>
       <c r="AH154" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI154" t="n">
         <v>100</v>
@@ -21298,7 +21298,7 @@
         <v>1</v>
       </c>
       <c r="AH155" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI155" t="n">
         <v>100</v>
@@ -21433,7 +21433,7 @@
         <v>1</v>
       </c>
       <c r="AH156" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI156" t="n">
         <v>100</v>
@@ -21568,7 +21568,7 @@
         <v>0.4</v>
       </c>
       <c r="AH157" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI157" t="n">
         <v>100</v>
@@ -21703,7 +21703,7 @@
         <v>1</v>
       </c>
       <c r="AH158" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI158" t="n">
         <v>100</v>
@@ -21838,7 +21838,7 @@
         <v>0.08</v>
       </c>
       <c r="AH159" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI159" t="n">
         <v>100</v>
@@ -21973,7 +21973,7 @@
         <v>1</v>
       </c>
       <c r="AH160" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI160" t="n">
         <v>100</v>
@@ -22108,7 +22108,7 @@
         <v>1</v>
       </c>
       <c r="AH161" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI161" t="n">
         <v>100</v>
@@ -22243,7 +22243,7 @@
         <v>1</v>
       </c>
       <c r="AH162" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI162" t="n">
         <v>100</v>
@@ -22378,7 +22378,7 @@
         <v>1</v>
       </c>
       <c r="AH163" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI163" t="n">
         <v>100</v>
@@ -22513,7 +22513,7 @@
         <v>0.4</v>
       </c>
       <c r="AH164" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI164" t="n">
         <v>100</v>
@@ -22648,7 +22648,7 @@
         <v>1</v>
       </c>
       <c r="AH165" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI165" t="n">
         <v>100</v>
@@ -22783,7 +22783,7 @@
         <v>1</v>
       </c>
       <c r="AH166" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI166" t="n">
         <v>100</v>
@@ -22918,7 +22918,7 @@
         <v>1</v>
       </c>
       <c r="AH167" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI167" t="n">
         <v>100</v>
@@ -23053,7 +23053,7 @@
         <v>1</v>
       </c>
       <c r="AH168" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI168" t="n">
         <v>100</v>
@@ -23188,7 +23188,7 @@
         <v>0.4</v>
       </c>
       <c r="AH169" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI169" t="n">
         <v>100</v>
@@ -23323,7 +23323,7 @@
         <v>1</v>
       </c>
       <c r="AH170" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI170" t="n">
         <v>100</v>
@@ -23458,7 +23458,7 @@
         <v>1</v>
       </c>
       <c r="AH171" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI171" t="n">
         <v>100</v>
@@ -23593,7 +23593,7 @@
         <v>1</v>
       </c>
       <c r="AH172" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI172" t="n">
         <v>100</v>
@@ -23728,7 +23728,7 @@
         <v>1</v>
       </c>
       <c r="AH173" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI173" t="n">
         <v>100</v>
@@ -23863,7 +23863,7 @@
         <v>0.4</v>
       </c>
       <c r="AH174" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI174" t="n">
         <v>100</v>
@@ -23998,7 +23998,7 @@
         <v>1</v>
       </c>
       <c r="AH175" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI175" t="n">
         <v>100</v>
@@ -24133,7 +24133,7 @@
         <v>0.08</v>
       </c>
       <c r="AH176" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI176" t="n">
         <v>100</v>
@@ -24268,7 +24268,7 @@
         <v>1</v>
       </c>
       <c r="AH177" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI177" t="n">
         <v>100</v>
@@ -24403,7 +24403,7 @@
         <v>1</v>
       </c>
       <c r="AH178" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI178" t="n">
         <v>100</v>
@@ -24538,7 +24538,7 @@
         <v>1</v>
       </c>
       <c r="AH179" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI179" t="n">
         <v>100</v>
@@ -24673,7 +24673,7 @@
         <v>1</v>
       </c>
       <c r="AH180" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI180" t="n">
         <v>100</v>
@@ -24808,7 +24808,7 @@
         <v>0.4</v>
       </c>
       <c r="AH181" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI181" t="n">
         <v>100</v>
@@ -24943,7 +24943,7 @@
         <v>1</v>
       </c>
       <c r="AH182" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI182" t="n">
         <v>100</v>
@@ -25078,7 +25078,7 @@
         <v>1</v>
       </c>
       <c r="AH183" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI183" t="n">
         <v>100</v>
@@ -25213,7 +25213,7 @@
         <v>1</v>
       </c>
       <c r="AH184" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI184" t="n">
         <v>100</v>
@@ -25348,7 +25348,7 @@
         <v>1</v>
       </c>
       <c r="AH185" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI185" t="n">
         <v>100</v>
@@ -25483,7 +25483,7 @@
         <v>0.4</v>
       </c>
       <c r="AH186" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI186" t="n">
         <v>100</v>
@@ -25618,7 +25618,7 @@
         <v>1</v>
       </c>
       <c r="AH187" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI187" t="n">
         <v>100</v>
@@ -25753,7 +25753,7 @@
         <v>1</v>
       </c>
       <c r="AH188" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI188" t="n">
         <v>100</v>
@@ -25888,7 +25888,7 @@
         <v>1</v>
       </c>
       <c r="AH189" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI189" t="n">
         <v>100</v>
@@ -26023,7 +26023,7 @@
         <v>1</v>
       </c>
       <c r="AH190" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI190" t="n">
         <v>100</v>
@@ -26158,7 +26158,7 @@
         <v>0.4</v>
       </c>
       <c r="AH191" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI191" t="n">
         <v>100</v>
@@ -26293,7 +26293,7 @@
         <v>1</v>
       </c>
       <c r="AH192" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI192" t="n">
         <v>100</v>
@@ -26428,7 +26428,7 @@
         <v>0.08</v>
       </c>
       <c r="AH193" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI193" t="n">
         <v>100</v>
@@ -26563,7 +26563,7 @@
         <v>1</v>
       </c>
       <c r="AH194" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI194" t="n">
         <v>100</v>
@@ -26698,7 +26698,7 @@
         <v>1</v>
       </c>
       <c r="AH195" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI195" t="n">
         <v>100</v>
@@ -26833,7 +26833,7 @@
         <v>1</v>
       </c>
       <c r="AH196" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI196" t="n">
         <v>100</v>
@@ -26968,7 +26968,7 @@
         <v>1</v>
       </c>
       <c r="AH197" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI197" t="n">
         <v>100</v>
@@ -27103,7 +27103,7 @@
         <v>0.4</v>
       </c>
       <c r="AH198" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI198" t="n">
         <v>100</v>
@@ -27238,7 +27238,7 @@
         <v>1</v>
       </c>
       <c r="AH199" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI199" t="n">
         <v>100</v>
@@ -27373,7 +27373,7 @@
         <v>1</v>
       </c>
       <c r="AH200" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI200" t="n">
         <v>100</v>
@@ -27508,7 +27508,7 @@
         <v>1</v>
       </c>
       <c r="AH201" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI201" t="n">
         <v>100</v>
@@ -27643,7 +27643,7 @@
         <v>1</v>
       </c>
       <c r="AH202" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI202" t="n">
         <v>100</v>
@@ -27778,7 +27778,7 @@
         <v>0.4</v>
       </c>
       <c r="AH203" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI203" t="n">
         <v>100</v>
@@ -27913,7 +27913,7 @@
         <v>1</v>
       </c>
       <c r="AH204" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI204" t="n">
         <v>100</v>
@@ -28048,7 +28048,7 @@
         <v>1</v>
       </c>
       <c r="AH205" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI205" t="n">
         <v>100</v>
@@ -28183,7 +28183,7 @@
         <v>1</v>
       </c>
       <c r="AH206" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI206" t="n">
         <v>100</v>
@@ -28318,7 +28318,7 @@
         <v>1</v>
       </c>
       <c r="AH207" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI207" t="n">
         <v>100</v>
@@ -28453,7 +28453,7 @@
         <v>0.4</v>
       </c>
       <c r="AH208" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI208" t="n">
         <v>100</v>
@@ -28588,7 +28588,7 @@
         <v>1</v>
       </c>
       <c r="AH209" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI209" t="n">
         <v>100</v>
@@ -28723,7 +28723,7 @@
         <v>0.08</v>
       </c>
       <c r="AH210" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI210" t="n">
         <v>100</v>
@@ -28858,7 +28858,7 @@
         <v>1</v>
       </c>
       <c r="AH211" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI211" t="n">
         <v>100</v>
@@ -28993,7 +28993,7 @@
         <v>1</v>
       </c>
       <c r="AH212" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI212" t="n">
         <v>100</v>
@@ -29128,7 +29128,7 @@
         <v>1</v>
       </c>
       <c r="AH213" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI213" t="n">
         <v>100</v>
@@ -29263,7 +29263,7 @@
         <v>1</v>
       </c>
       <c r="AH214" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI214" t="n">
         <v>100</v>
@@ -29398,7 +29398,7 @@
         <v>0.4</v>
       </c>
       <c r="AH215" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI215" t="n">
         <v>100</v>
@@ -29533,7 +29533,7 @@
         <v>1</v>
       </c>
       <c r="AH216" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI216" t="n">
         <v>100</v>
@@ -29668,7 +29668,7 @@
         <v>1</v>
       </c>
       <c r="AH217" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI217" t="n">
         <v>100</v>
@@ -29803,7 +29803,7 @@
         <v>1</v>
       </c>
       <c r="AH218" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI218" t="n">
         <v>100</v>
@@ -29938,7 +29938,7 @@
         <v>1</v>
       </c>
       <c r="AH219" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI219" t="n">
         <v>100</v>
@@ -30073,7 +30073,7 @@
         <v>0.4</v>
       </c>
       <c r="AH220" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI220" t="n">
         <v>100</v>
@@ -30208,7 +30208,7 @@
         <v>1</v>
       </c>
       <c r="AH221" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI221" t="n">
         <v>100</v>
@@ -30343,7 +30343,7 @@
         <v>1</v>
       </c>
       <c r="AH222" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI222" t="n">
         <v>100</v>
@@ -30478,7 +30478,7 @@
         <v>1</v>
       </c>
       <c r="AH223" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI223" t="n">
         <v>100</v>
@@ -30613,7 +30613,7 @@
         <v>1</v>
       </c>
       <c r="AH224" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI224" t="n">
         <v>100</v>
@@ -30748,7 +30748,7 @@
         <v>0.4</v>
       </c>
       <c r="AH225" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI225" t="n">
         <v>100</v>
@@ -30883,7 +30883,7 @@
         <v>1</v>
       </c>
       <c r="AH226" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI226" t="n">
         <v>100</v>
@@ -31018,7 +31018,7 @@
         <v>0.08</v>
       </c>
       <c r="AH227" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI227" t="n">
         <v>100</v>
@@ -31153,7 +31153,7 @@
         <v>1</v>
       </c>
       <c r="AH228" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI228" t="n">
         <v>100</v>
@@ -31288,7 +31288,7 @@
         <v>1</v>
       </c>
       <c r="AH229" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI229" t="n">
         <v>100</v>
@@ -31423,7 +31423,7 @@
         <v>1</v>
       </c>
       <c r="AH230" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI230" t="n">
         <v>100</v>
@@ -31558,7 +31558,7 @@
         <v>1</v>
       </c>
       <c r="AH231" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI231" t="n">
         <v>100</v>
@@ -31693,7 +31693,7 @@
         <v>0.4</v>
       </c>
       <c r="AH232" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI232" t="n">
         <v>100</v>
@@ -31828,7 +31828,7 @@
         <v>1</v>
       </c>
       <c r="AH233" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI233" t="n">
         <v>100</v>
@@ -31963,7 +31963,7 @@
         <v>1</v>
       </c>
       <c r="AH234" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI234" t="n">
         <v>100</v>
@@ -32098,7 +32098,7 @@
         <v>1</v>
       </c>
       <c r="AH235" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI235" t="n">
         <v>100</v>
@@ -32233,7 +32233,7 @@
         <v>1</v>
       </c>
       <c r="AH236" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI236" t="n">
         <v>100</v>
@@ -32368,7 +32368,7 @@
         <v>0.4</v>
       </c>
       <c r="AH237" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI237" t="n">
         <v>100</v>
@@ -32503,7 +32503,7 @@
         <v>1</v>
       </c>
       <c r="AH238" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI238" t="n">
         <v>100</v>
@@ -32638,7 +32638,7 @@
         <v>1</v>
       </c>
       <c r="AH239" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI239" t="n">
         <v>100</v>
@@ -32773,7 +32773,7 @@
         <v>1</v>
       </c>
       <c r="AH240" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI240" t="n">
         <v>100</v>
@@ -32908,7 +32908,7 @@
         <v>1</v>
       </c>
       <c r="AH241" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI241" t="n">
         <v>100</v>
@@ -33043,7 +33043,7 @@
         <v>0.4</v>
       </c>
       <c r="AH242" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI242" t="n">
         <v>100</v>
@@ -33178,7 +33178,7 @@
         <v>1</v>
       </c>
       <c r="AH243" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI243" t="n">
         <v>100</v>
@@ -33313,7 +33313,7 @@
         <v>0.08</v>
       </c>
       <c r="AH244" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI244" t="n">
         <v>100</v>
@@ -33448,7 +33448,7 @@
         <v>1</v>
       </c>
       <c r="AH245" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI245" t="n">
         <v>100</v>
@@ -33583,7 +33583,7 @@
         <v>1</v>
       </c>
       <c r="AH246" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI246" t="n">
         <v>100</v>
@@ -33718,7 +33718,7 @@
         <v>1</v>
       </c>
       <c r="AH247" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI247" t="n">
         <v>100</v>
@@ -33853,7 +33853,7 @@
         <v>1</v>
       </c>
       <c r="AH248" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI248" t="n">
         <v>100</v>
@@ -33988,7 +33988,7 @@
         <v>0.4</v>
       </c>
       <c r="AH249" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI249" t="n">
         <v>100</v>
@@ -34123,7 +34123,7 @@
         <v>1</v>
       </c>
       <c r="AH250" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI250" t="n">
         <v>100</v>
@@ -34258,7 +34258,7 @@
         <v>1</v>
       </c>
       <c r="AH251" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI251" t="n">
         <v>100</v>
@@ -34393,7 +34393,7 @@
         <v>1</v>
       </c>
       <c r="AH252" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI252" t="n">
         <v>100</v>
@@ -34528,7 +34528,7 @@
         <v>1</v>
       </c>
       <c r="AH253" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI253" t="n">
         <v>100</v>
@@ -34663,7 +34663,7 @@
         <v>0.4</v>
       </c>
       <c r="AH254" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI254" t="n">
         <v>100</v>
@@ -34798,7 +34798,7 @@
         <v>1</v>
       </c>
       <c r="AH255" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI255" t="n">
         <v>100</v>
@@ -34933,7 +34933,7 @@
         <v>1</v>
       </c>
       <c r="AH256" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI256" t="n">
         <v>100</v>
@@ -35068,7 +35068,7 @@
         <v>1</v>
       </c>
       <c r="AH257" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI257" t="n">
         <v>100</v>
@@ -35203,7 +35203,7 @@
         <v>1</v>
       </c>
       <c r="AH258" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI258" t="n">
         <v>100</v>
@@ -35338,7 +35338,7 @@
         <v>0.4</v>
       </c>
       <c r="AH259" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI259" t="n">
         <v>100</v>
@@ -35473,7 +35473,7 @@
         <v>1</v>
       </c>
       <c r="AH260" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI260" t="n">
         <v>100</v>
@@ -35608,7 +35608,7 @@
         <v>0.08</v>
       </c>
       <c r="AH261" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI261" t="n">
         <v>100</v>
@@ -35743,7 +35743,7 @@
         <v>1</v>
       </c>
       <c r="AH262" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI262" t="n">
         <v>100</v>
@@ -35878,7 +35878,7 @@
         <v>1</v>
       </c>
       <c r="AH263" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI263" t="n">
         <v>100</v>
@@ -36013,7 +36013,7 @@
         <v>1</v>
       </c>
       <c r="AH264" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI264" t="n">
         <v>100</v>
@@ -36148,7 +36148,7 @@
         <v>1</v>
       </c>
       <c r="AH265" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI265" t="n">
         <v>100</v>
@@ -36283,7 +36283,7 @@
         <v>0.4</v>
       </c>
       <c r="AH266" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI266" t="n">
         <v>100</v>
@@ -36418,7 +36418,7 @@
         <v>1</v>
       </c>
       <c r="AH267" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI267" t="n">
         <v>100</v>
@@ -36553,7 +36553,7 @@
         <v>1</v>
       </c>
       <c r="AH268" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI268" t="n">
         <v>100</v>
@@ -36688,7 +36688,7 @@
         <v>1</v>
       </c>
       <c r="AH269" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI269" t="n">
         <v>100</v>
@@ -36823,7 +36823,7 @@
         <v>1</v>
       </c>
       <c r="AH270" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI270" t="n">
         <v>100</v>
@@ -36958,7 +36958,7 @@
         <v>0.4</v>
       </c>
       <c r="AH271" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI271" t="n">
         <v>100</v>
@@ -37093,7 +37093,7 @@
         <v>1</v>
       </c>
       <c r="AH272" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI272" t="n">
         <v>100</v>
@@ -37228,7 +37228,7 @@
         <v>1</v>
       </c>
       <c r="AH273" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI273" t="n">
         <v>100</v>
@@ -37363,7 +37363,7 @@
         <v>1</v>
       </c>
       <c r="AH274" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI274" t="n">
         <v>100</v>
@@ -37498,7 +37498,7 @@
         <v>1</v>
       </c>
       <c r="AH275" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI275" t="n">
         <v>100</v>
@@ -37633,7 +37633,7 @@
         <v>0.4</v>
       </c>
       <c r="AH276" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI276" t="n">
         <v>100</v>
@@ -37768,7 +37768,7 @@
         <v>1</v>
       </c>
       <c r="AH277" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI277" t="n">
         <v>100</v>
@@ -37903,7 +37903,7 @@
         <v>0.08</v>
       </c>
       <c r="AH278" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI278" t="n">
         <v>100</v>
@@ -38038,7 +38038,7 @@
         <v>1</v>
       </c>
       <c r="AH279" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI279" t="n">
         <v>100</v>
@@ -38173,7 +38173,7 @@
         <v>1</v>
       </c>
       <c r="AH280" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI280" t="n">
         <v>100</v>
@@ -38308,7 +38308,7 @@
         <v>1</v>
       </c>
       <c r="AH281" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI281" t="n">
         <v>100</v>
@@ -38443,7 +38443,7 @@
         <v>1</v>
       </c>
       <c r="AH282" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI282" t="n">
         <v>100</v>
@@ -38578,7 +38578,7 @@
         <v>0.4</v>
       </c>
       <c r="AH283" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI283" t="n">
         <v>100</v>
@@ -38713,7 +38713,7 @@
         <v>1</v>
       </c>
       <c r="AH284" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI284" t="n">
         <v>100</v>
@@ -38848,7 +38848,7 @@
         <v>1</v>
       </c>
       <c r="AH285" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI285" t="n">
         <v>100</v>
@@ -38983,7 +38983,7 @@
         <v>1</v>
       </c>
       <c r="AH286" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI286" t="n">
         <v>100</v>
@@ -39118,7 +39118,7 @@
         <v>1</v>
       </c>
       <c r="AH287" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI287" t="n">
         <v>100</v>
@@ -39253,7 +39253,7 @@
         <v>0.4</v>
       </c>
       <c r="AH288" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI288" t="n">
         <v>100</v>
@@ -39388,7 +39388,7 @@
         <v>1</v>
       </c>
       <c r="AH289" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI289" t="n">
         <v>100</v>
@@ -39523,7 +39523,7 @@
         <v>1</v>
       </c>
       <c r="AH290" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI290" t="n">
         <v>100</v>
@@ -39658,7 +39658,7 @@
         <v>1</v>
       </c>
       <c r="AH291" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI291" t="n">
         <v>100</v>
@@ -39793,7 +39793,7 @@
         <v>1</v>
       </c>
       <c r="AH292" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI292" t="n">
         <v>100</v>
@@ -39928,7 +39928,7 @@
         <v>0.4</v>
       </c>
       <c r="AH293" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI293" t="n">
         <v>100</v>
@@ -40063,7 +40063,7 @@
         <v>1</v>
       </c>
       <c r="AH294" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI294" t="n">
         <v>100</v>
@@ -40198,7 +40198,7 @@
         <v>0.08</v>
       </c>
       <c r="AH295" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI295" t="n">
         <v>100</v>
@@ -40333,7 +40333,7 @@
         <v>1</v>
       </c>
       <c r="AH296" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI296" t="n">
         <v>100</v>
@@ -40468,7 +40468,7 @@
         <v>1</v>
       </c>
       <c r="AH297" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI297" t="n">
         <v>100</v>
@@ -40603,7 +40603,7 @@
         <v>1</v>
       </c>
       <c r="AH298" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI298" t="n">
         <v>100</v>
@@ -40738,7 +40738,7 @@
         <v>1</v>
       </c>
       <c r="AH299" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI299" t="n">
         <v>100</v>
@@ -40873,7 +40873,7 @@
         <v>0.4</v>
       </c>
       <c r="AH300" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI300" t="n">
         <v>100</v>
@@ -41008,7 +41008,7 @@
         <v>1</v>
       </c>
       <c r="AH301" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI301" t="n">
         <v>100</v>
@@ -41143,7 +41143,7 @@
         <v>1</v>
       </c>
       <c r="AH302" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI302" t="n">
         <v>100</v>
@@ -41278,7 +41278,7 @@
         <v>1</v>
       </c>
       <c r="AH303" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI303" t="n">
         <v>100</v>
@@ -41413,7 +41413,7 @@
         <v>1</v>
       </c>
       <c r="AH304" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI304" t="n">
         <v>100</v>
@@ -41548,7 +41548,7 @@
         <v>0.4</v>
       </c>
       <c r="AH305" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI305" t="n">
         <v>100</v>
@@ -41683,7 +41683,7 @@
         <v>1</v>
       </c>
       <c r="AH306" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI306" t="n">
         <v>100</v>
@@ -41818,7 +41818,7 @@
         <v>1</v>
       </c>
       <c r="AH307" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI307" t="n">
         <v>100</v>
@@ -41953,7 +41953,7 @@
         <v>1</v>
       </c>
       <c r="AH308" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI308" t="n">
         <v>100</v>
@@ -42088,7 +42088,7 @@
         <v>1</v>
       </c>
       <c r="AH309" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI309" t="n">
         <v>100</v>
@@ -42223,7 +42223,7 @@
         <v>0.4</v>
       </c>
       <c r="AH310" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI310" t="n">
         <v>100</v>
@@ -42358,7 +42358,7 @@
         <v>1</v>
       </c>
       <c r="AH311" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI311" t="n">
         <v>100</v>
@@ -42493,7 +42493,7 @@
         <v>0.08</v>
       </c>
       <c r="AH312" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI312" t="n">
         <v>100</v>
@@ -42628,7 +42628,7 @@
         <v>1</v>
       </c>
       <c r="AH313" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI313" t="n">
         <v>100</v>
@@ -42763,7 +42763,7 @@
         <v>1</v>
       </c>
       <c r="AH314" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI314" t="n">
         <v>100</v>
@@ -42898,7 +42898,7 @@
         <v>1</v>
       </c>
       <c r="AH315" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI315" t="n">
         <v>100</v>
@@ -43033,7 +43033,7 @@
         <v>1</v>
       </c>
       <c r="AH316" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI316" t="n">
         <v>100</v>
@@ -43168,7 +43168,7 @@
         <v>0.4</v>
       </c>
       <c r="AH317" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI317" t="n">
         <v>100</v>
@@ -43303,7 +43303,7 @@
         <v>1</v>
       </c>
       <c r="AH318" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI318" t="n">
         <v>100</v>
@@ -43438,7 +43438,7 @@
         <v>1</v>
       </c>
       <c r="AH319" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI319" t="n">
         <v>100</v>
@@ -43573,7 +43573,7 @@
         <v>1</v>
       </c>
       <c r="AH320" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI320" t="n">
         <v>100</v>
@@ -43708,7 +43708,7 @@
         <v>1</v>
       </c>
       <c r="AH321" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI321" t="n">
         <v>100</v>
@@ -43843,7 +43843,7 @@
         <v>0.4</v>
       </c>
       <c r="AH322" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI322" t="n">
         <v>100</v>
@@ -43978,7 +43978,7 @@
         <v>1</v>
       </c>
       <c r="AH323" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI323" t="n">
         <v>100</v>
@@ -44113,7 +44113,7 @@
         <v>1</v>
       </c>
       <c r="AH324" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI324" t="n">
         <v>100</v>
@@ -44248,7 +44248,7 @@
         <v>1</v>
       </c>
       <c r="AH325" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI325" t="n">
         <v>100</v>
@@ -44383,7 +44383,7 @@
         <v>1</v>
       </c>
       <c r="AH326" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI326" t="n">
         <v>100</v>
@@ -44518,7 +44518,7 @@
         <v>0.4</v>
       </c>
       <c r="AH327" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI327" t="n">
         <v>100</v>
@@ -44653,7 +44653,7 @@
         <v>1</v>
       </c>
       <c r="AH328" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI328" t="n">
         <v>100</v>
@@ -44788,7 +44788,7 @@
         <v>0.08</v>
       </c>
       <c r="AH329" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI329" t="n">
         <v>100</v>
@@ -44923,7 +44923,7 @@
         <v>1</v>
       </c>
       <c r="AH330" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI330" t="n">
         <v>100</v>
@@ -45058,7 +45058,7 @@
         <v>1</v>
       </c>
       <c r="AH331" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI331" t="n">
         <v>100</v>
@@ -45193,7 +45193,7 @@
         <v>1</v>
       </c>
       <c r="AH332" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI332" t="n">
         <v>100</v>
@@ -45328,7 +45328,7 @@
         <v>1</v>
       </c>
       <c r="AH333" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI333" t="n">
         <v>100</v>
@@ -45463,7 +45463,7 @@
         <v>0.4</v>
       </c>
       <c r="AH334" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI334" t="n">
         <v>100</v>
@@ -45598,7 +45598,7 @@
         <v>1</v>
       </c>
       <c r="AH335" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI335" t="n">
         <v>100</v>
@@ -45733,7 +45733,7 @@
         <v>1</v>
       </c>
       <c r="AH336" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI336" t="n">
         <v>100</v>
@@ -45868,7 +45868,7 @@
         <v>1</v>
       </c>
       <c r="AH337" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI337" t="n">
         <v>100</v>
@@ -46003,7 +46003,7 @@
         <v>1</v>
       </c>
       <c r="AH338" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI338" t="n">
         <v>100</v>
@@ -46138,7 +46138,7 @@
         <v>0.4</v>
       </c>
       <c r="AH339" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI339" t="n">
         <v>100</v>
@@ -46273,7 +46273,7 @@
         <v>1</v>
       </c>
       <c r="AH340" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI340" t="n">
         <v>100</v>
@@ -46408,7 +46408,7 @@
         <v>1</v>
       </c>
       <c r="AH341" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI341" t="n">
         <v>100</v>
@@ -46543,7 +46543,7 @@
         <v>1</v>
       </c>
       <c r="AH342" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI342" t="n">
         <v>100</v>
@@ -46678,7 +46678,7 @@
         <v>1</v>
       </c>
       <c r="AH343" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI343" t="n">
         <v>100</v>
@@ -46813,7 +46813,7 @@
         <v>0.4</v>
       </c>
       <c r="AH344" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI344" t="n">
         <v>100</v>
@@ -46948,7 +46948,7 @@
         <v>1</v>
       </c>
       <c r="AH345" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI345" t="n">
         <v>100</v>
@@ -47083,7 +47083,7 @@
         <v>0.08</v>
       </c>
       <c r="AH346" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI346" t="n">
         <v>100</v>
@@ -47218,7 +47218,7 @@
         <v>1</v>
       </c>
       <c r="AH347" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI347" t="n">
         <v>100</v>
@@ -47353,7 +47353,7 @@
         <v>1</v>
       </c>
       <c r="AH348" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI348" t="n">
         <v>100</v>
@@ -47488,7 +47488,7 @@
         <v>1</v>
       </c>
       <c r="AH349" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI349" t="n">
         <v>100</v>
@@ -47623,7 +47623,7 @@
         <v>1</v>
       </c>
       <c r="AH350" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI350" t="n">
         <v>100</v>
@@ -47758,7 +47758,7 @@
         <v>0.4</v>
       </c>
       <c r="AH351" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI351" t="n">
         <v>100</v>
@@ -47893,7 +47893,7 @@
         <v>1</v>
       </c>
       <c r="AH352" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI352" t="n">
         <v>100</v>
@@ -48028,7 +48028,7 @@
         <v>1</v>
       </c>
       <c r="AH353" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI353" t="n">
         <v>100</v>
@@ -48163,7 +48163,7 @@
         <v>1</v>
       </c>
       <c r="AH354" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI354" t="n">
         <v>100</v>
@@ -48298,7 +48298,7 @@
         <v>1</v>
       </c>
       <c r="AH355" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI355" t="n">
         <v>100</v>
@@ -48433,7 +48433,7 @@
         <v>0.4</v>
       </c>
       <c r="AH356" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI356" t="n">
         <v>100</v>
@@ -48568,7 +48568,7 @@
         <v>1</v>
       </c>
       <c r="AH357" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI357" t="n">
         <v>100</v>
@@ -48703,7 +48703,7 @@
         <v>1</v>
       </c>
       <c r="AH358" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI358" t="n">
         <v>100</v>
@@ -48838,7 +48838,7 @@
         <v>1</v>
       </c>
       <c r="AH359" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI359" t="n">
         <v>100</v>
@@ -48973,7 +48973,7 @@
         <v>1</v>
       </c>
       <c r="AH360" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI360" t="n">
         <v>100</v>
@@ -49108,7 +49108,7 @@
         <v>0.4</v>
       </c>
       <c r="AH361" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI361" t="n">
         <v>100</v>
@@ -49243,7 +49243,7 @@
         <v>0.08</v>
       </c>
       <c r="AH362" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI362" t="n">
         <v>100</v>
@@ -49378,7 +49378,7 @@
         <v>1</v>
       </c>
       <c r="AH363" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI363" t="n">
         <v>100</v>
@@ -49513,7 +49513,7 @@
         <v>1</v>
       </c>
       <c r="AH364" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI364" t="n">
         <v>100</v>
@@ -49648,7 +49648,7 @@
         <v>1</v>
       </c>
       <c r="AH365" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI365" t="n">
         <v>100</v>
@@ -49783,7 +49783,7 @@
         <v>1</v>
       </c>
       <c r="AH366" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI366" t="n">
         <v>100</v>
@@ -49918,7 +49918,7 @@
         <v>0.4</v>
       </c>
       <c r="AH367" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI367" t="n">
         <v>100</v>
@@ -50053,7 +50053,7 @@
         <v>1</v>
       </c>
       <c r="AH368" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI368" t="n">
         <v>100</v>
@@ -50188,7 +50188,7 @@
         <v>1</v>
       </c>
       <c r="AH369" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI369" t="n">
         <v>100</v>
@@ -50323,7 +50323,7 @@
         <v>1</v>
       </c>
       <c r="AH370" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI370" t="n">
         <v>100</v>
@@ -50458,7 +50458,7 @@
         <v>1</v>
       </c>
       <c r="AH371" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI371" t="n">
         <v>100</v>
@@ -50593,7 +50593,7 @@
         <v>0.4</v>
       </c>
       <c r="AH372" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI372" t="n">
         <v>100</v>
@@ -50728,7 +50728,7 @@
         <v>1</v>
       </c>
       <c r="AH373" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI373" t="n">
         <v>100</v>
@@ -50863,7 +50863,7 @@
         <v>1</v>
       </c>
       <c r="AH374" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI374" t="n">
         <v>100</v>
@@ -50998,7 +50998,7 @@
         <v>1</v>
       </c>
       <c r="AH375" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI375" t="n">
         <v>100</v>
@@ -51133,7 +51133,7 @@
         <v>1</v>
       </c>
       <c r="AH376" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI376" t="n">
         <v>100</v>
@@ -51268,7 +51268,7 @@
         <v>0.4</v>
       </c>
       <c r="AH377" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI377" t="n">
         <v>100</v>
@@ -51403,7 +51403,7 @@
         <v>0.08</v>
       </c>
       <c r="AH378" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI378" t="n">
         <v>100</v>
@@ -51538,7 +51538,7 @@
         <v>1</v>
       </c>
       <c r="AH379" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI379" t="n">
         <v>100</v>
@@ -51673,7 +51673,7 @@
         <v>1</v>
       </c>
       <c r="AH380" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI380" t="n">
         <v>100</v>
@@ -51808,7 +51808,7 @@
         <v>1</v>
       </c>
       <c r="AH381" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI381" t="n">
         <v>100</v>
@@ -51943,7 +51943,7 @@
         <v>1</v>
       </c>
       <c r="AH382" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI382" t="n">
         <v>100</v>
@@ -52078,7 +52078,7 @@
         <v>0.4</v>
       </c>
       <c r="AH383" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI383" t="n">
         <v>100</v>
@@ -52213,7 +52213,7 @@
         <v>1</v>
       </c>
       <c r="AH384" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI384" t="n">
         <v>100</v>
@@ -52348,7 +52348,7 @@
         <v>1</v>
       </c>
       <c r="AH385" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI385" t="n">
         <v>100</v>
@@ -52483,7 +52483,7 @@
         <v>1</v>
       </c>
       <c r="AH386" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI386" t="n">
         <v>100</v>
@@ -52618,7 +52618,7 @@
         <v>1</v>
       </c>
       <c r="AH387" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI387" t="n">
         <v>100</v>
@@ -52753,7 +52753,7 @@
         <v>0.4</v>
       </c>
       <c r="AH388" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI388" t="n">
         <v>100</v>
@@ -52888,7 +52888,7 @@
         <v>1</v>
       </c>
       <c r="AH389" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI389" t="n">
         <v>100</v>
@@ -53023,7 +53023,7 @@
         <v>1</v>
       </c>
       <c r="AH390" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI390" t="n">
         <v>100</v>
@@ -53158,7 +53158,7 @@
         <v>1</v>
       </c>
       <c r="AH391" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI391" t="n">
         <v>100</v>
@@ -53293,7 +53293,7 @@
         <v>1</v>
       </c>
       <c r="AH392" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI392" t="n">
         <v>100</v>
@@ -53428,7 +53428,7 @@
         <v>0.4</v>
       </c>
       <c r="AH393" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI393" t="n">
         <v>100</v>
@@ -53563,7 +53563,7 @@
         <v>0.08</v>
       </c>
       <c r="AH394" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI394" t="n">
         <v>100</v>
@@ -53698,7 +53698,7 @@
         <v>1</v>
       </c>
       <c r="AH395" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI395" t="n">
         <v>100</v>
@@ -53833,7 +53833,7 @@
         <v>1</v>
       </c>
       <c r="AH396" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI396" t="n">
         <v>100</v>
@@ -53968,7 +53968,7 @@
         <v>1</v>
       </c>
       <c r="AH397" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI397" t="n">
         <v>100</v>
@@ -54103,7 +54103,7 @@
         <v>1</v>
       </c>
       <c r="AH398" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI398" t="n">
         <v>100</v>
@@ -54238,7 +54238,7 @@
         <v>0.4</v>
       </c>
       <c r="AH399" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI399" t="n">
         <v>100</v>
@@ -54373,7 +54373,7 @@
         <v>1</v>
       </c>
       <c r="AH400" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI400" t="n">
         <v>100</v>
@@ -54508,7 +54508,7 @@
         <v>1</v>
       </c>
       <c r="AH401" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI401" t="n">
         <v>100</v>
@@ -54643,7 +54643,7 @@
         <v>1</v>
       </c>
       <c r="AH402" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI402" t="n">
         <v>100</v>
@@ -54778,7 +54778,7 @@
         <v>1</v>
       </c>
       <c r="AH403" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI403" t="n">
         <v>100</v>
@@ -54913,7 +54913,7 @@
         <v>0.4</v>
       </c>
       <c r="AH404" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI404" t="n">
         <v>100</v>
@@ -55048,7 +55048,7 @@
         <v>1</v>
       </c>
       <c r="AH405" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI405" t="n">
         <v>100</v>
@@ -55183,7 +55183,7 @@
         <v>1</v>
       </c>
       <c r="AH406" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI406" t="n">
         <v>100</v>
@@ -55318,7 +55318,7 @@
         <v>1</v>
       </c>
       <c r="AH407" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI407" t="n">
         <v>100</v>
@@ -55453,7 +55453,7 @@
         <v>1</v>
       </c>
       <c r="AH408" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI408" t="n">
         <v>100</v>
@@ -55588,7 +55588,7 @@
         <v>0.4</v>
       </c>
       <c r="AH409" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI409" t="n">
         <v>100</v>
@@ -55723,7 +55723,7 @@
         <v>0.08</v>
       </c>
       <c r="AH410" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI410" t="n">
         <v>100</v>
@@ -55858,7 +55858,7 @@
         <v>1</v>
       </c>
       <c r="AH411" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI411" t="n">
         <v>100</v>
@@ -55993,7 +55993,7 @@
         <v>1</v>
       </c>
       <c r="AH412" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI412" t="n">
         <v>100</v>
@@ -56128,7 +56128,7 @@
         <v>1</v>
       </c>
       <c r="AH413" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI413" t="n">
         <v>100</v>
@@ -56263,7 +56263,7 @@
         <v>1</v>
       </c>
       <c r="AH414" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI414" t="n">
         <v>100</v>
@@ -56398,7 +56398,7 @@
         <v>0.4</v>
       </c>
       <c r="AH415" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI415" t="n">
         <v>100</v>
@@ -56533,7 +56533,7 @@
         <v>1</v>
       </c>
       <c r="AH416" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI416" t="n">
         <v>100</v>
@@ -56668,7 +56668,7 @@
         <v>1</v>
       </c>
       <c r="AH417" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI417" t="n">
         <v>100</v>
@@ -56803,7 +56803,7 @@
         <v>1</v>
       </c>
       <c r="AH418" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI418" t="n">
         <v>100</v>
@@ -56938,7 +56938,7 @@
         <v>1</v>
       </c>
       <c r="AH419" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI419" t="n">
         <v>100</v>
@@ -57073,7 +57073,7 @@
         <v>0.4</v>
       </c>
       <c r="AH420" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI420" t="n">
         <v>100</v>
@@ -57208,7 +57208,7 @@
         <v>1</v>
       </c>
       <c r="AH421" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI421" t="n">
         <v>100</v>
@@ -57343,7 +57343,7 @@
         <v>1</v>
       </c>
       <c r="AH422" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI422" t="n">
         <v>100</v>
@@ -57478,7 +57478,7 @@
         <v>1</v>
       </c>
       <c r="AH423" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI423" t="n">
         <v>100</v>
@@ -57613,7 +57613,7 @@
         <v>1</v>
       </c>
       <c r="AH424" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI424" t="n">
         <v>100</v>
@@ -57748,7 +57748,7 @@
         <v>0.4</v>
       </c>
       <c r="AH425" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI425" t="n">
         <v>100</v>
@@ -57883,7 +57883,7 @@
         <v>0.08</v>
       </c>
       <c r="AH426" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI426" t="n">
         <v>100</v>
@@ -58018,7 +58018,7 @@
         <v>1</v>
       </c>
       <c r="AH427" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI427" t="n">
         <v>100</v>
@@ -58153,7 +58153,7 @@
         <v>1</v>
       </c>
       <c r="AH428" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI428" t="n">
         <v>100</v>
@@ -58288,7 +58288,7 @@
         <v>1</v>
       </c>
       <c r="AH429" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI429" t="n">
         <v>100</v>
@@ -58423,7 +58423,7 @@
         <v>1</v>
       </c>
       <c r="AH430" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI430" t="n">
         <v>100</v>
@@ -58558,7 +58558,7 @@
         <v>0.4</v>
       </c>
       <c r="AH431" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI431" t="n">
         <v>100</v>
@@ -58693,7 +58693,7 @@
         <v>1</v>
       </c>
       <c r="AH432" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI432" t="n">
         <v>100</v>
@@ -58828,7 +58828,7 @@
         <v>1</v>
       </c>
       <c r="AH433" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI433" t="n">
         <v>100</v>
@@ -58963,7 +58963,7 @@
         <v>1</v>
       </c>
       <c r="AH434" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI434" t="n">
         <v>100</v>
@@ -59098,7 +59098,7 @@
         <v>1</v>
       </c>
       <c r="AH435" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI435" t="n">
         <v>100</v>
@@ -59233,7 +59233,7 @@
         <v>0.4</v>
       </c>
       <c r="AH436" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI436" t="n">
         <v>100</v>
@@ -59368,7 +59368,7 @@
         <v>1</v>
       </c>
       <c r="AH437" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI437" t="n">
         <v>100</v>
@@ -59503,7 +59503,7 @@
         <v>1</v>
       </c>
       <c r="AH438" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI438" t="n">
         <v>100</v>
@@ -59638,7 +59638,7 @@
         <v>1</v>
       </c>
       <c r="AH439" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI439" t="n">
         <v>100</v>
@@ -59773,7 +59773,7 @@
         <v>1</v>
       </c>
       <c r="AH440" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI440" t="n">
         <v>100</v>
@@ -59908,7 +59908,7 @@
         <v>0.4</v>
       </c>
       <c r="AH441" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI441" t="n">
         <v>100</v>
@@ -60043,7 +60043,7 @@
         <v>0.08</v>
       </c>
       <c r="AH442" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI442" t="n">
         <v>100</v>
@@ -60178,7 +60178,7 @@
         <v>1</v>
       </c>
       <c r="AH443" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI443" t="n">
         <v>100</v>
@@ -60313,7 +60313,7 @@
         <v>1</v>
       </c>
       <c r="AH444" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI444" t="n">
         <v>100</v>
@@ -60448,7 +60448,7 @@
         <v>1</v>
       </c>
       <c r="AH445" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI445" t="n">
         <v>100</v>
@@ -60583,7 +60583,7 @@
         <v>1</v>
       </c>
       <c r="AH446" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI446" t="n">
         <v>100</v>
@@ -60718,7 +60718,7 @@
         <v>0.4</v>
       </c>
       <c r="AH447" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI447" t="n">
         <v>100</v>
@@ -60853,7 +60853,7 @@
         <v>1</v>
       </c>
       <c r="AH448" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI448" t="n">
         <v>100</v>
@@ -60988,7 +60988,7 @@
         <v>1</v>
       </c>
       <c r="AH449" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI449" t="n">
         <v>100</v>
@@ -61123,7 +61123,7 @@
         <v>1</v>
       </c>
       <c r="AH450" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI450" t="n">
         <v>100</v>
@@ -61258,7 +61258,7 @@
         <v>1</v>
       </c>
       <c r="AH451" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI451" t="n">
         <v>100</v>
@@ -61393,7 +61393,7 @@
         <v>0.4</v>
       </c>
       <c r="AH452" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI452" t="n">
         <v>100</v>
@@ -61528,7 +61528,7 @@
         <v>1</v>
       </c>
       <c r="AH453" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI453" t="n">
         <v>100</v>
@@ -61663,7 +61663,7 @@
         <v>1</v>
       </c>
       <c r="AH454" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI454" t="n">
         <v>100</v>
@@ -61798,7 +61798,7 @@
         <v>1</v>
       </c>
       <c r="AH455" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI455" t="n">
         <v>100</v>
@@ -61933,7 +61933,7 @@
         <v>1</v>
       </c>
       <c r="AH456" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI456" t="n">
         <v>100</v>
@@ -62068,7 +62068,7 @@
         <v>0.4</v>
       </c>
       <c r="AH457" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI457" t="n">
         <v>100</v>
@@ -62203,7 +62203,7 @@
         <v>0.08</v>
       </c>
       <c r="AH458" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI458" t="n">
         <v>100</v>
@@ -62338,7 +62338,7 @@
         <v>1</v>
       </c>
       <c r="AH459" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI459" t="n">
         <v>100</v>
@@ -62473,7 +62473,7 @@
         <v>1</v>
       </c>
       <c r="AH460" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI460" t="n">
         <v>100</v>
@@ -62608,7 +62608,7 @@
         <v>1</v>
       </c>
       <c r="AH461" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI461" t="n">
         <v>100</v>
@@ -62743,7 +62743,7 @@
         <v>1</v>
       </c>
       <c r="AH462" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI462" t="n">
         <v>100</v>
@@ -62878,7 +62878,7 @@
         <v>0.4</v>
       </c>
       <c r="AH463" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI463" t="n">
         <v>100</v>
@@ -63013,7 +63013,7 @@
         <v>1</v>
       </c>
       <c r="AH464" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI464" t="n">
         <v>100</v>
@@ -63148,7 +63148,7 @@
         <v>1</v>
       </c>
       <c r="AH465" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI465" t="n">
         <v>100</v>
@@ -63283,7 +63283,7 @@
         <v>1</v>
       </c>
       <c r="AH466" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI466" t="n">
         <v>100</v>
@@ -63418,7 +63418,7 @@
         <v>1</v>
       </c>
       <c r="AH467" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI467" t="n">
         <v>100</v>
@@ -63553,7 +63553,7 @@
         <v>0.4</v>
       </c>
       <c r="AH468" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI468" t="n">
         <v>100</v>
@@ -63688,7 +63688,7 @@
         <v>1</v>
       </c>
       <c r="AH469" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI469" t="n">
         <v>100</v>
@@ -63823,7 +63823,7 @@
         <v>1</v>
       </c>
       <c r="AH470" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI470" t="n">
         <v>100</v>
@@ -63958,7 +63958,7 @@
         <v>1</v>
       </c>
       <c r="AH471" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI471" t="n">
         <v>100</v>
@@ -64093,7 +64093,7 @@
         <v>1</v>
       </c>
       <c r="AH472" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI472" t="n">
         <v>100</v>
@@ -64228,7 +64228,7 @@
         <v>0.4</v>
       </c>
       <c r="AH473" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI473" t="n">
         <v>100</v>
@@ -64363,7 +64363,7 @@
         <v>0.08</v>
       </c>
       <c r="AH474" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI474" t="n">
         <v>100</v>
@@ -64498,7 +64498,7 @@
         <v>1</v>
       </c>
       <c r="AH475" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI475" t="n">
         <v>100</v>
@@ -64633,7 +64633,7 @@
         <v>1</v>
       </c>
       <c r="AH476" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI476" t="n">
         <v>100</v>
@@ -64768,7 +64768,7 @@
         <v>1</v>
       </c>
       <c r="AH477" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI477" t="n">
         <v>100</v>
@@ -64903,7 +64903,7 @@
         <v>1</v>
       </c>
       <c r="AH478" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI478" t="n">
         <v>100</v>
@@ -65038,7 +65038,7 @@
         <v>0.4</v>
       </c>
       <c r="AH479" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI479" t="n">
         <v>100</v>
@@ -65173,7 +65173,7 @@
         <v>1</v>
       </c>
       <c r="AH480" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI480" t="n">
         <v>100</v>
@@ -65308,7 +65308,7 @@
         <v>1</v>
       </c>
       <c r="AH481" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI481" t="n">
         <v>100</v>
@@ -65443,7 +65443,7 @@
         <v>1</v>
       </c>
       <c r="AH482" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI482" t="n">
         <v>100</v>
@@ -65578,7 +65578,7 @@
         <v>1</v>
       </c>
       <c r="AH483" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI483" t="n">
         <v>100</v>
@@ -65713,7 +65713,7 @@
         <v>0.4</v>
       </c>
       <c r="AH484" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI484" t="n">
         <v>100</v>
@@ -65848,7 +65848,7 @@
         <v>1</v>
       </c>
       <c r="AH485" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI485" t="n">
         <v>100</v>
@@ -65983,7 +65983,7 @@
         <v>1</v>
       </c>
       <c r="AH486" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI486" t="n">
         <v>100</v>
@@ -66118,7 +66118,7 @@
         <v>1</v>
       </c>
       <c r="AH487" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI487" t="n">
         <v>100</v>
@@ -66253,7 +66253,7 @@
         <v>1</v>
       </c>
       <c r="AH488" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI488" t="n">
         <v>100</v>
@@ -66388,7 +66388,7 @@
         <v>0.4</v>
       </c>
       <c r="AH489" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI489" t="n">
         <v>100</v>
@@ -66523,7 +66523,7 @@
         <v>0.08</v>
       </c>
       <c r="AH490" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI490" t="n">
         <v>100</v>
@@ -66658,7 +66658,7 @@
         <v>1</v>
       </c>
       <c r="AH491" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI491" t="n">
         <v>100</v>
@@ -66793,7 +66793,7 @@
         <v>1</v>
       </c>
       <c r="AH492" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI492" t="n">
         <v>100</v>
@@ -66928,7 +66928,7 @@
         <v>1</v>
       </c>
       <c r="AH493" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI493" t="n">
         <v>100</v>
@@ -67063,7 +67063,7 @@
         <v>1</v>
       </c>
       <c r="AH494" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI494" t="n">
         <v>100</v>
@@ -67198,7 +67198,7 @@
         <v>0.4</v>
       </c>
       <c r="AH495" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI495" t="n">
         <v>100</v>
@@ -67333,7 +67333,7 @@
         <v>1</v>
       </c>
       <c r="AH496" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI496" t="n">
         <v>100</v>
@@ -67468,7 +67468,7 @@
         <v>1</v>
       </c>
       <c r="AH497" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI497" t="n">
         <v>100</v>
@@ -67603,7 +67603,7 @@
         <v>1</v>
       </c>
       <c r="AH498" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI498" t="n">
         <v>100</v>
@@ -67738,7 +67738,7 @@
         <v>1</v>
       </c>
       <c r="AH499" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI499" t="n">
         <v>100</v>
@@ -67873,7 +67873,7 @@
         <v>0.4</v>
       </c>
       <c r="AH500" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI500" t="n">
         <v>100</v>
@@ -68008,7 +68008,7 @@
         <v>1</v>
       </c>
       <c r="AH501" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI501" t="n">
         <v>100</v>
@@ -68143,7 +68143,7 @@
         <v>1</v>
       </c>
       <c r="AH502" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI502" t="n">
         <v>100</v>
@@ -68278,7 +68278,7 @@
         <v>1</v>
       </c>
       <c r="AH503" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI503" t="n">
         <v>100</v>
@@ -68413,7 +68413,7 @@
         <v>1</v>
       </c>
       <c r="AH504" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AI504" t="n">
         <v>100</v>
@@ -68548,7 +68548,7 @@
         <v>0.4</v>
       </c>
       <c r="AH505" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI505" t="n">
         <v>100</v>
@@ -68683,7 +68683,7 @@
         <v>0.08</v>
       </c>
       <c r="AH506" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI506" t="n">
         <v>100</v>

--- a/Assets/@Resources/Data/Excel/CreatureData.xlsx
+++ b/Assets/@Resources/Data/Excel/CreatureData.xlsx
@@ -806,7 +806,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2001</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2002</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>goblin_monster_0.sprite</t>
+          <t>Mon_2003</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2101</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2102</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2103</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2104</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2105</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2106</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2107</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_7</t>
+          <t>Mon_2108</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_8</t>
+          <t>Mon_2109</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_9</t>
+          <t>Mon_2110</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2111</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2112</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2113</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2114</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2115</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2116</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2117</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2118</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2119</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2120</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2121</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2122</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2123</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2124</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_7</t>
+          <t>Mon_2125</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_8</t>
+          <t>Mon_2126</t>
         </is>
       </c>
       <c r="E32" t="n">

--- a/Assets/@Resources/Data/Excel/CreatureData.xlsx
+++ b/Assets/@Resources/Data/Excel/CreatureData.xlsx
@@ -828,7 +828,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>11001</v>
+        <v>10001</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -963,7 +963,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>11001</v>
+        <v>10002</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>

--- a/Assets/@Resources/Data/Excel/CreatureData.xlsx
+++ b/Assets/@Resources/Data/Excel/CreatureData.xlsx
@@ -4721,7 +4721,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_9</t>
+          <t>Mon_2127</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2128</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2129</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2130</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2131</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2132</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2133</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2134</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2135</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2136</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2137</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2138</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2139</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2140</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2141</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_7</t>
+          <t>Mon_2142</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_8</t>
+          <t>Mon_2143</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_9</t>
+          <t>Mon_2144</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2145</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2146</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2147</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2148</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2149</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2150</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2151</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2152</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2153</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2154</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2155</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2156</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2157</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2158</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_7</t>
+          <t>Mon_2159</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_8</t>
+          <t>Mon_2160</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_9</t>
+          <t>Mon_2161</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2162</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2163</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2164</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2165</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2166</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2167</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2168</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2169</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2170</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2171</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2172</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2173</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2174</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2175</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_7</t>
+          <t>Mon_2176</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_8</t>
+          <t>Mon_2177</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_9</t>
+          <t>Mon_2178</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2179</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2180</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2181</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2182</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2183</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2184</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -12551,7 +12551,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2185</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2186</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2187</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2188</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2189</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2190</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2191</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2192</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_7</t>
+          <t>Mon_2193</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_8</t>
+          <t>Mon_2194</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_9</t>
+          <t>Mon_2195</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -14036,7 +14036,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2196</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2197</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2198</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2199</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2200</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2201</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -14846,7 +14846,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2202</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2203</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2204</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2205</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -15386,7 +15386,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2206</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -15521,7 +15521,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2207</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2208</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2209</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_7</t>
+          <t>Mon_2210</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_8</t>
+          <t>Mon_2211</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_9</t>
+          <t>Mon_2212</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2213</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2214</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -16601,7 +16601,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2215</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -16736,7 +16736,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2216</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -16871,7 +16871,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2217</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2218</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2219</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -17276,7 +17276,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2220</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -17411,7 +17411,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2221</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -17546,7 +17546,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2222</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -17681,7 +17681,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2223</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2224</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -17951,7 +17951,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2225</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2226</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -18221,7 +18221,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_7</t>
+          <t>Mon_2227</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -18356,7 +18356,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_8</t>
+          <t>Mon_2228</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_9</t>
+          <t>Mon_2229</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -18626,7 +18626,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2230</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -18761,7 +18761,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2231</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -18896,7 +18896,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2232</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -19031,7 +19031,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2233</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2234</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -19301,7 +19301,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2235</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -19436,7 +19436,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2236</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -19571,7 +19571,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2237</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -19706,7 +19706,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2238</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2239</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -19976,7 +19976,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2240</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2241</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -20246,7 +20246,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2242</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -20381,7 +20381,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2243</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_7</t>
+          <t>Mon_2244</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_8</t>
+          <t>Mon_2245</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -20786,7 +20786,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_9</t>
+          <t>Mon_2246</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -20921,7 +20921,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2247</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -21056,7 +21056,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2248</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2249</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2250</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -21461,7 +21461,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2251</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2252</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -21731,7 +21731,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2253</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -21866,7 +21866,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2254</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -22001,7 +22001,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2255</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2256</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -22271,7 +22271,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2257</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -22406,7 +22406,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2258</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -22541,7 +22541,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2259</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -22676,7 +22676,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2260</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -22811,7 +22811,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_7</t>
+          <t>Mon_2261</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_8</t>
+          <t>Mon_2262</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -23081,7 +23081,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_9</t>
+          <t>Mon_2263</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -23216,7 +23216,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_0</t>
+          <t>Mon_2264</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_1</t>
+          <t>Mon_2265</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -23486,7 +23486,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_2</t>
+          <t>Mon_2266</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -23621,7 +23621,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_3</t>
+          <t>Mon_2267</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -23756,7 +23756,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_4</t>
+          <t>Mon_2268</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -23891,7 +23891,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_5</t>
+          <t>Mon_2269</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -24026,7 +24026,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Mon_BreezingWindForest_6</t>
+          <t>Mon_2270</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -24161,7 +24161,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2271</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -24296,7 +24296,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2272</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -24431,7 +24431,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2273</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -24566,7 +24566,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2274</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -24701,7 +24701,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2275</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -24836,7 +24836,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2276</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2277</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -25106,7 +25106,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_7</t>
+          <t>Mon_2278</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -25241,7 +25241,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_8</t>
+          <t>Mon_2279</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_9</t>
+          <t>Mon_2280</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2281</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -25646,7 +25646,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2282</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -25781,7 +25781,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2283</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -25916,7 +25916,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2284</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -26051,7 +26051,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2285</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -26186,7 +26186,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2286</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -26321,7 +26321,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2287</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2288</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -26591,7 +26591,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2289</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -26726,7 +26726,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2290</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -26861,7 +26861,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2291</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -26996,7 +26996,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2292</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2293</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2294</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -27401,7 +27401,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_7</t>
+          <t>Mon_2295</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_8</t>
+          <t>Mon_2296</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -27671,7 +27671,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_9</t>
+          <t>Mon_2297</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -27806,7 +27806,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2298</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -27941,7 +27941,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2299</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -28076,7 +28076,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2300</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -28211,7 +28211,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2301</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2302</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -28481,7 +28481,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2303</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -28616,7 +28616,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2304</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -28751,7 +28751,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2305</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -28886,7 +28886,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2306</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -29021,7 +29021,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2307</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -29156,7 +29156,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2308</t>
         </is>
       </c>
       <c r="E214" t="n">
@@ -29291,7 +29291,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2309</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -29426,7 +29426,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2310</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -29561,7 +29561,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2311</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -29696,7 +29696,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_7</t>
+          <t>Mon_2312</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -29831,7 +29831,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_8</t>
+          <t>Mon_2313</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -29966,7 +29966,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_9</t>
+          <t>Mon_2314</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -30101,7 +30101,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2315</t>
         </is>
       </c>
       <c r="E221" t="n">
@@ -30236,7 +30236,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2316</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -30371,7 +30371,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2317</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -30506,7 +30506,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2318</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -30641,7 +30641,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2319</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -30776,7 +30776,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2320</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -30911,7 +30911,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2321</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -31046,7 +31046,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2322</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -31181,7 +31181,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2323</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -31316,7 +31316,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2324</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -31451,7 +31451,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2325</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -31586,7 +31586,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2326</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -31721,7 +31721,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2327</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -31856,7 +31856,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2328</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -31991,7 +31991,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_7</t>
+          <t>Mon_2329</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -32126,7 +32126,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_8</t>
+          <t>Mon_2330</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -32261,7 +32261,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_9</t>
+          <t>Mon_2331</t>
         </is>
       </c>
       <c r="E237" t="n">
@@ -32396,7 +32396,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2332</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -32531,7 +32531,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2333</t>
         </is>
       </c>
       <c r="E239" t="n">
@@ -32666,7 +32666,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2334</t>
         </is>
       </c>
       <c r="E240" t="n">
@@ -32801,7 +32801,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2335</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -32936,7 +32936,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2336</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -33071,7 +33071,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2337</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -33206,7 +33206,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2338</t>
         </is>
       </c>
       <c r="E244" t="n">
@@ -33341,7 +33341,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2339</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2340</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -33611,7 +33611,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2341</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -33746,7 +33746,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2342</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -33881,7 +33881,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2343</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -34016,7 +34016,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2344</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -34151,7 +34151,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2345</t>
         </is>
       </c>
       <c r="E251" t="n">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_7</t>
+          <t>Mon_2346</t>
         </is>
       </c>
       <c r="E252" t="n">
@@ -34421,7 +34421,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_8</t>
+          <t>Mon_2347</t>
         </is>
       </c>
       <c r="E253" t="n">
@@ -34556,7 +34556,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_9</t>
+          <t>Mon_2348</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -34691,7 +34691,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2349</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -34826,7 +34826,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2350</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -34961,7 +34961,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2351</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -35096,7 +35096,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2352</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -35231,7 +35231,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2353</t>
         </is>
       </c>
       <c r="E259" t="n">
@@ -35366,7 +35366,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2354</t>
         </is>
       </c>
       <c r="E260" t="n">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2355</t>
         </is>
       </c>
       <c r="E261" t="n">
@@ -35636,7 +35636,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2356</t>
         </is>
       </c>
       <c r="E262" t="n">
@@ -35771,7 +35771,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2357</t>
         </is>
       </c>
       <c r="E263" t="n">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2358</t>
         </is>
       </c>
       <c r="E264" t="n">
@@ -36041,7 +36041,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2359</t>
         </is>
       </c>
       <c r="E265" t="n">
@@ -36176,7 +36176,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2360</t>
         </is>
       </c>
       <c r="E266" t="n">
@@ -36311,7 +36311,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2361</t>
         </is>
       </c>
       <c r="E267" t="n">
@@ -36446,7 +36446,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2362</t>
         </is>
       </c>
       <c r="E268" t="n">
@@ -36581,7 +36581,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_7</t>
+          <t>Mon_2363</t>
         </is>
       </c>
       <c r="E269" t="n">
@@ -36716,7 +36716,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_8</t>
+          <t>Mon_2364</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -36851,7 +36851,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_9</t>
+          <t>Mon_2365</t>
         </is>
       </c>
       <c r="E271" t="n">
@@ -36986,7 +36986,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2366</t>
         </is>
       </c>
       <c r="E272" t="n">
@@ -37121,7 +37121,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2367</t>
         </is>
       </c>
       <c r="E273" t="n">
@@ -37256,7 +37256,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2368</t>
         </is>
       </c>
       <c r="E274" t="n">
@@ -37391,7 +37391,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2369</t>
         </is>
       </c>
       <c r="E275" t="n">
@@ -37526,7 +37526,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2370</t>
         </is>
       </c>
       <c r="E276" t="n">
@@ -37661,7 +37661,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2371</t>
         </is>
       </c>
       <c r="E277" t="n">
@@ -37796,7 +37796,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2372</t>
         </is>
       </c>
       <c r="E278" t="n">
@@ -37931,7 +37931,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2373</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -38066,7 +38066,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2374</t>
         </is>
       </c>
       <c r="E280" t="n">
@@ -38201,7 +38201,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2375</t>
         </is>
       </c>
       <c r="E281" t="n">
@@ -38336,7 +38336,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2376</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -38471,7 +38471,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2377</t>
         </is>
       </c>
       <c r="E283" t="n">
@@ -38606,7 +38606,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2378</t>
         </is>
       </c>
       <c r="E284" t="n">
@@ -38741,7 +38741,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2379</t>
         </is>
       </c>
       <c r="E285" t="n">
@@ -38876,7 +38876,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_7</t>
+          <t>Mon_2380</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -39011,7 +39011,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_8</t>
+          <t>Mon_2381</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -39146,7 +39146,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_9</t>
+          <t>Mon_2382</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -39281,7 +39281,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2383</t>
         </is>
       </c>
       <c r="E289" t="n">
@@ -39416,7 +39416,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2384</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -39551,7 +39551,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2385</t>
         </is>
       </c>
       <c r="E291" t="n">
@@ -39686,7 +39686,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2386</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -39821,7 +39821,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2387</t>
         </is>
       </c>
       <c r="E293" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2388</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -40091,7 +40091,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2389</t>
         </is>
       </c>
       <c r="E295" t="n">
@@ -40226,7 +40226,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2390</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -40361,7 +40361,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2391</t>
         </is>
       </c>
       <c r="E297" t="n">
@@ -40496,7 +40496,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2392</t>
         </is>
       </c>
       <c r="E298" t="n">
@@ -40631,7 +40631,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2393</t>
         </is>
       </c>
       <c r="E299" t="n">
@@ -40766,7 +40766,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2394</t>
         </is>
       </c>
       <c r="E300" t="n">
@@ -40901,7 +40901,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2395</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -41036,7 +41036,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2396</t>
         </is>
       </c>
       <c r="E302" t="n">
@@ -41171,7 +41171,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_7</t>
+          <t>Mon_2397</t>
         </is>
       </c>
       <c r="E303" t="n">
@@ -41306,7 +41306,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_8</t>
+          <t>Mon_2398</t>
         </is>
       </c>
       <c r="E304" t="n">
@@ -41441,7 +41441,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_9</t>
+          <t>Mon_2399</t>
         </is>
       </c>
       <c r="E305" t="n">
@@ -41576,7 +41576,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2400</t>
         </is>
       </c>
       <c r="E306" t="n">
@@ -41711,7 +41711,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2401</t>
         </is>
       </c>
       <c r="E307" t="n">
@@ -41846,7 +41846,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2402</t>
         </is>
       </c>
       <c r="E308" t="n">
@@ -41981,7 +41981,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2403</t>
         </is>
       </c>
       <c r="E309" t="n">
@@ -42116,7 +42116,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2404</t>
         </is>
       </c>
       <c r="E310" t="n">
@@ -42251,7 +42251,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2405</t>
         </is>
       </c>
       <c r="E311" t="n">
@@ -42386,7 +42386,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2406</t>
         </is>
       </c>
       <c r="E312" t="n">
@@ -42521,7 +42521,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2407</t>
         </is>
       </c>
       <c r="E313" t="n">
@@ -42656,7 +42656,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2408</t>
         </is>
       </c>
       <c r="E314" t="n">
@@ -42791,7 +42791,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2409</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -42926,7 +42926,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2410</t>
         </is>
       </c>
       <c r="E316" t="n">
@@ -43061,7 +43061,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2411</t>
         </is>
       </c>
       <c r="E317" t="n">
@@ -43196,7 +43196,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2412</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -43331,7 +43331,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2413</t>
         </is>
       </c>
       <c r="E319" t="n">
@@ -43466,7 +43466,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_7</t>
+          <t>Mon_2414</t>
         </is>
       </c>
       <c r="E320" t="n">
@@ -43601,7 +43601,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_8</t>
+          <t>Mon_2415</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -43736,7 +43736,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_9</t>
+          <t>Mon_2416</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -43871,7 +43871,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2417</t>
         </is>
       </c>
       <c r="E323" t="n">
@@ -44006,7 +44006,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2418</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -44141,7 +44141,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2419</t>
         </is>
       </c>
       <c r="E325" t="n">
@@ -44276,7 +44276,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2420</t>
         </is>
       </c>
       <c r="E326" t="n">
@@ -44411,7 +44411,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2421</t>
         </is>
       </c>
       <c r="E327" t="n">
@@ -44546,7 +44546,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2422</t>
         </is>
       </c>
       <c r="E328" t="n">
@@ -44681,7 +44681,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2423</t>
         </is>
       </c>
       <c r="E329" t="n">
@@ -44816,7 +44816,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2424</t>
         </is>
       </c>
       <c r="E330" t="n">
@@ -44951,7 +44951,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2425</t>
         </is>
       </c>
       <c r="E331" t="n">
@@ -45086,7 +45086,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2426</t>
         </is>
       </c>
       <c r="E332" t="n">
@@ -45221,7 +45221,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2427</t>
         </is>
       </c>
       <c r="E333" t="n">
@@ -45356,7 +45356,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2428</t>
         </is>
       </c>
       <c r="E334" t="n">
@@ -45491,7 +45491,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2429</t>
         </is>
       </c>
       <c r="E335" t="n">
@@ -45626,7 +45626,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2430</t>
         </is>
       </c>
       <c r="E336" t="n">
@@ -45761,7 +45761,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_7</t>
+          <t>Mon_2431</t>
         </is>
       </c>
       <c r="E337" t="n">
@@ -45896,7 +45896,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_8</t>
+          <t>Mon_2432</t>
         </is>
       </c>
       <c r="E338" t="n">
@@ -46031,7 +46031,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_9</t>
+          <t>Mon_2433</t>
         </is>
       </c>
       <c r="E339" t="n">
@@ -46166,7 +46166,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_0</t>
+          <t>Mon_2434</t>
         </is>
       </c>
       <c r="E340" t="n">
@@ -46301,7 +46301,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_1</t>
+          <t>Mon_2435</t>
         </is>
       </c>
       <c r="E341" t="n">
@@ -46436,7 +46436,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_2</t>
+          <t>Mon_2436</t>
         </is>
       </c>
       <c r="E342" t="n">
@@ -46571,7 +46571,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_3</t>
+          <t>Mon_2437</t>
         </is>
       </c>
       <c r="E343" t="n">
@@ -46706,7 +46706,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_4</t>
+          <t>Mon_2438</t>
         </is>
       </c>
       <c r="E344" t="n">
@@ -46841,7 +46841,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_5</t>
+          <t>Mon_2439</t>
         </is>
       </c>
       <c r="E345" t="n">
@@ -46976,7 +46976,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Mon_WhisperingCave_6</t>
+          <t>Mon_2440</t>
         </is>
       </c>
       <c r="E346" t="n">
@@ -47111,7 +47111,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2441</t>
         </is>
       </c>
       <c r="E347" t="n">
@@ -47246,7 +47246,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2442</t>
         </is>
       </c>
       <c r="E348" t="n">
@@ -47381,7 +47381,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2443</t>
         </is>
       </c>
       <c r="E349" t="n">
@@ -47516,7 +47516,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2444</t>
         </is>
       </c>
       <c r="E350" t="n">
@@ -47651,7 +47651,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2445</t>
         </is>
       </c>
       <c r="E351" t="n">
@@ -47786,7 +47786,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2446</t>
         </is>
       </c>
       <c r="E352" t="n">
@@ -47921,7 +47921,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_6</t>
+          <t>Mon_2447</t>
         </is>
       </c>
       <c r="E353" t="n">
@@ -48056,7 +48056,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_7</t>
+          <t>Mon_2448</t>
         </is>
       </c>
       <c r="E354" t="n">
@@ -48191,7 +48191,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_8</t>
+          <t>Mon_2449</t>
         </is>
       </c>
       <c r="E355" t="n">
@@ -48326,7 +48326,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_9</t>
+          <t>Mon_2450</t>
         </is>
       </c>
       <c r="E356" t="n">
@@ -48461,7 +48461,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2451</t>
         </is>
       </c>
       <c r="E357" t="n">
@@ -48596,7 +48596,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2452</t>
         </is>
       </c>
       <c r="E358" t="n">
@@ -48731,7 +48731,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2453</t>
         </is>
       </c>
       <c r="E359" t="n">
@@ -48866,7 +48866,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2454</t>
         </is>
       </c>
       <c r="E360" t="n">
@@ -49001,7 +49001,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2455</t>
         </is>
       </c>
       <c r="E361" t="n">
@@ -49136,7 +49136,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2456</t>
         </is>
       </c>
       <c r="E362" t="n">
@@ -49271,7 +49271,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2457</t>
         </is>
       </c>
       <c r="E363" t="n">
@@ -49406,7 +49406,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2458</t>
         </is>
       </c>
       <c r="E364" t="n">
@@ -49541,7 +49541,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2459</t>
         </is>
       </c>
       <c r="E365" t="n">
@@ -49676,7 +49676,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2460</t>
         </is>
       </c>
       <c r="E366" t="n">
@@ -49811,7 +49811,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2461</t>
         </is>
       </c>
       <c r="E367" t="n">
@@ -49946,7 +49946,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2462</t>
         </is>
       </c>
       <c r="E368" t="n">
@@ -50081,7 +50081,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_6</t>
+          <t>Mon_2463</t>
         </is>
       </c>
       <c r="E369" t="n">
@@ -50216,7 +50216,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_7</t>
+          <t>Mon_2464</t>
         </is>
       </c>
       <c r="E370" t="n">
@@ -50351,7 +50351,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_8</t>
+          <t>Mon_2465</t>
         </is>
       </c>
       <c r="E371" t="n">
@@ -50486,7 +50486,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_9</t>
+          <t>Mon_2466</t>
         </is>
       </c>
       <c r="E372" t="n">
@@ -50621,7 +50621,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2467</t>
         </is>
       </c>
       <c r="E373" t="n">
@@ -50756,7 +50756,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2468</t>
         </is>
       </c>
       <c r="E374" t="n">
@@ -50891,7 +50891,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2469</t>
         </is>
       </c>
       <c r="E375" t="n">
@@ -51026,7 +51026,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2470</t>
         </is>
       </c>
       <c r="E376" t="n">
@@ -51161,7 +51161,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2471</t>
         </is>
       </c>
       <c r="E377" t="n">
@@ -51296,7 +51296,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2472</t>
         </is>
       </c>
       <c r="E378" t="n">
@@ -51431,7 +51431,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2473</t>
         </is>
       </c>
       <c r="E379" t="n">
@@ -51566,7 +51566,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2474</t>
         </is>
       </c>
       <c r="E380" t="n">
@@ -51701,7 +51701,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2475</t>
         </is>
       </c>
       <c r="E381" t="n">
@@ -51836,7 +51836,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2476</t>
         </is>
       </c>
       <c r="E382" t="n">
@@ -51971,7 +51971,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2477</t>
         </is>
       </c>
       <c r="E383" t="n">
@@ -52106,7 +52106,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2478</t>
         </is>
       </c>
       <c r="E384" t="n">
@@ -52241,7 +52241,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_6</t>
+          <t>Mon_2479</t>
         </is>
       </c>
       <c r="E385" t="n">
@@ -52376,7 +52376,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_7</t>
+          <t>Mon_2480</t>
         </is>
       </c>
       <c r="E386" t="n">
@@ -52511,7 +52511,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_8</t>
+          <t>Mon_2481</t>
         </is>
       </c>
       <c r="E387" t="n">
@@ -52646,7 +52646,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_9</t>
+          <t>Mon_2482</t>
         </is>
       </c>
       <c r="E388" t="n">
@@ -52781,7 +52781,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2483</t>
         </is>
       </c>
       <c r="E389" t="n">
@@ -52916,7 +52916,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2484</t>
         </is>
       </c>
       <c r="E390" t="n">
@@ -53051,7 +53051,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2485</t>
         </is>
       </c>
       <c r="E391" t="n">
@@ -53186,7 +53186,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2486</t>
         </is>
       </c>
       <c r="E392" t="n">
@@ -53321,7 +53321,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2487</t>
         </is>
       </c>
       <c r="E393" t="n">
@@ -53456,7 +53456,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2488</t>
         </is>
       </c>
       <c r="E394" t="n">
@@ -53591,7 +53591,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2489</t>
         </is>
       </c>
       <c r="E395" t="n">
@@ -53726,7 +53726,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2490</t>
         </is>
       </c>
       <c r="E396" t="n">
@@ -53861,7 +53861,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2491</t>
         </is>
       </c>
       <c r="E397" t="n">
@@ -53996,7 +53996,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2492</t>
         </is>
       </c>
       <c r="E398" t="n">
@@ -54131,7 +54131,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2493</t>
         </is>
       </c>
       <c r="E399" t="n">
@@ -54266,7 +54266,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2494</t>
         </is>
       </c>
       <c r="E400" t="n">
@@ -54401,7 +54401,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_6</t>
+          <t>Mon_2495</t>
         </is>
       </c>
       <c r="E401" t="n">
@@ -54536,7 +54536,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_7</t>
+          <t>Mon_2496</t>
         </is>
       </c>
       <c r="E402" t="n">
@@ -54671,7 +54671,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_8</t>
+          <t>Mon_2497</t>
         </is>
       </c>
       <c r="E403" t="n">
@@ -54806,7 +54806,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_9</t>
+          <t>Mon_2498</t>
         </is>
       </c>
       <c r="E404" t="n">
@@ -54941,7 +54941,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2499</t>
         </is>
       </c>
       <c r="E405" t="n">
@@ -55076,7 +55076,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2500</t>
         </is>
       </c>
       <c r="E406" t="n">
@@ -55211,7 +55211,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2501</t>
         </is>
       </c>
       <c r="E407" t="n">
@@ -55346,7 +55346,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2502</t>
         </is>
       </c>
       <c r="E408" t="n">
@@ -55481,7 +55481,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2503</t>
         </is>
       </c>
       <c r="E409" t="n">
@@ -55616,7 +55616,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2504</t>
         </is>
       </c>
       <c r="E410" t="n">
@@ -55751,7 +55751,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2505</t>
         </is>
       </c>
       <c r="E411" t="n">
@@ -55886,7 +55886,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2506</t>
         </is>
       </c>
       <c r="E412" t="n">
@@ -56021,7 +56021,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2507</t>
         </is>
       </c>
       <c r="E413" t="n">
@@ -56156,7 +56156,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2508</t>
         </is>
       </c>
       <c r="E414" t="n">
@@ -56291,7 +56291,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2509</t>
         </is>
       </c>
       <c r="E415" t="n">
@@ -56426,7 +56426,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2510</t>
         </is>
       </c>
       <c r="E416" t="n">
@@ -56561,7 +56561,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_6</t>
+          <t>Mon_2511</t>
         </is>
       </c>
       <c r="E417" t="n">
@@ -56696,7 +56696,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_7</t>
+          <t>Mon_2512</t>
         </is>
       </c>
       <c r="E418" t="n">
@@ -56831,7 +56831,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_8</t>
+          <t>Mon_2513</t>
         </is>
       </c>
       <c r="E419" t="n">
@@ -56966,7 +56966,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_9</t>
+          <t>Mon_2514</t>
         </is>
       </c>
       <c r="E420" t="n">
@@ -57101,7 +57101,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2515</t>
         </is>
       </c>
       <c r="E421" t="n">
@@ -57236,7 +57236,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2516</t>
         </is>
       </c>
       <c r="E422" t="n">
@@ -57371,7 +57371,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2517</t>
         </is>
       </c>
       <c r="E423" t="n">
@@ -57506,7 +57506,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2518</t>
         </is>
       </c>
       <c r="E424" t="n">
@@ -57641,7 +57641,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2519</t>
         </is>
       </c>
       <c r="E425" t="n">
@@ -57776,7 +57776,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2520</t>
         </is>
       </c>
       <c r="E426" t="n">
@@ -57911,7 +57911,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2521</t>
         </is>
       </c>
       <c r="E427" t="n">
@@ -58046,7 +58046,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2522</t>
         </is>
       </c>
       <c r="E428" t="n">
@@ -58181,7 +58181,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2523</t>
         </is>
       </c>
       <c r="E429" t="n">
@@ -58316,7 +58316,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2524</t>
         </is>
       </c>
       <c r="E430" t="n">
@@ -58451,7 +58451,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2525</t>
         </is>
       </c>
       <c r="E431" t="n">
@@ -58586,7 +58586,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2526</t>
         </is>
       </c>
       <c r="E432" t="n">
@@ -58721,7 +58721,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_6</t>
+          <t>Mon_2527</t>
         </is>
       </c>
       <c r="E433" t="n">
@@ -58856,7 +58856,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_7</t>
+          <t>Mon_2528</t>
         </is>
       </c>
       <c r="E434" t="n">
@@ -58991,7 +58991,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_8</t>
+          <t>Mon_2529</t>
         </is>
       </c>
       <c r="E435" t="n">
@@ -59126,7 +59126,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_9</t>
+          <t>Mon_2530</t>
         </is>
       </c>
       <c r="E436" t="n">
@@ -59261,7 +59261,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2531</t>
         </is>
       </c>
       <c r="E437" t="n">
@@ -59396,7 +59396,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2532</t>
         </is>
       </c>
       <c r="E438" t="n">
@@ -59531,7 +59531,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2533</t>
         </is>
       </c>
       <c r="E439" t="n">
@@ -59666,7 +59666,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2534</t>
         </is>
       </c>
       <c r="E440" t="n">
@@ -59801,7 +59801,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2535</t>
         </is>
       </c>
       <c r="E441" t="n">
@@ -59936,7 +59936,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2536</t>
         </is>
       </c>
       <c r="E442" t="n">
@@ -60071,7 +60071,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2537</t>
         </is>
       </c>
       <c r="E443" t="n">
@@ -60206,7 +60206,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2538</t>
         </is>
       </c>
       <c r="E444" t="n">
@@ -60341,7 +60341,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2539</t>
         </is>
       </c>
       <c r="E445" t="n">
@@ -60476,7 +60476,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2540</t>
         </is>
       </c>
       <c r="E446" t="n">
@@ -60611,7 +60611,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2541</t>
         </is>
       </c>
       <c r="E447" t="n">
@@ -60746,7 +60746,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2542</t>
         </is>
       </c>
       <c r="E448" t="n">
@@ -60881,7 +60881,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_6</t>
+          <t>Mon_2543</t>
         </is>
       </c>
       <c r="E449" t="n">
@@ -61016,7 +61016,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_7</t>
+          <t>Mon_2544</t>
         </is>
       </c>
       <c r="E450" t="n">
@@ -61151,7 +61151,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_8</t>
+          <t>Mon_2545</t>
         </is>
       </c>
       <c r="E451" t="n">
@@ -61286,7 +61286,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_9</t>
+          <t>Mon_2546</t>
         </is>
       </c>
       <c r="E452" t="n">
@@ -61421,7 +61421,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2547</t>
         </is>
       </c>
       <c r="E453" t="n">
@@ -61556,7 +61556,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2548</t>
         </is>
       </c>
       <c r="E454" t="n">
@@ -61691,7 +61691,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2549</t>
         </is>
       </c>
       <c r="E455" t="n">
@@ -61826,7 +61826,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2550</t>
         </is>
       </c>
       <c r="E456" t="n">
@@ -61961,7 +61961,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2551</t>
         </is>
       </c>
       <c r="E457" t="n">
@@ -62096,7 +62096,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2552</t>
         </is>
       </c>
       <c r="E458" t="n">
@@ -62231,7 +62231,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2553</t>
         </is>
       </c>
       <c r="E459" t="n">
@@ -62366,7 +62366,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2554</t>
         </is>
       </c>
       <c r="E460" t="n">
@@ -62501,7 +62501,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2555</t>
         </is>
       </c>
       <c r="E461" t="n">
@@ -62636,7 +62636,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2556</t>
         </is>
       </c>
       <c r="E462" t="n">
@@ -62771,7 +62771,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2557</t>
         </is>
       </c>
       <c r="E463" t="n">
@@ -62906,7 +62906,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2558</t>
         </is>
       </c>
       <c r="E464" t="n">
@@ -63041,7 +63041,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_6</t>
+          <t>Mon_2559</t>
         </is>
       </c>
       <c r="E465" t="n">
@@ -63176,7 +63176,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_7</t>
+          <t>Mon_2560</t>
         </is>
       </c>
       <c r="E466" t="n">
@@ -63311,7 +63311,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_8</t>
+          <t>Mon_2561</t>
         </is>
       </c>
       <c r="E467" t="n">
@@ -63446,7 +63446,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_9</t>
+          <t>Mon_2562</t>
         </is>
       </c>
       <c r="E468" t="n">
@@ -63581,7 +63581,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2563</t>
         </is>
       </c>
       <c r="E469" t="n">
@@ -63716,7 +63716,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2564</t>
         </is>
       </c>
       <c r="E470" t="n">
@@ -63851,7 +63851,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2565</t>
         </is>
       </c>
       <c r="E471" t="n">
@@ -63986,7 +63986,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2566</t>
         </is>
       </c>
       <c r="E472" t="n">
@@ -64121,7 +64121,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2567</t>
         </is>
       </c>
       <c r="E473" t="n">
@@ -64256,7 +64256,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2568</t>
         </is>
       </c>
       <c r="E474" t="n">
@@ -64391,7 +64391,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2569</t>
         </is>
       </c>
       <c r="E475" t="n">
@@ -64526,7 +64526,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2570</t>
         </is>
       </c>
       <c r="E476" t="n">
@@ -64661,7 +64661,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2571</t>
         </is>
       </c>
       <c r="E477" t="n">
@@ -64796,7 +64796,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2572</t>
         </is>
       </c>
       <c r="E478" t="n">
@@ -64931,7 +64931,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2573</t>
         </is>
       </c>
       <c r="E479" t="n">
@@ -65066,7 +65066,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2574</t>
         </is>
       </c>
       <c r="E480" t="n">
@@ -65201,7 +65201,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_6</t>
+          <t>Mon_2575</t>
         </is>
       </c>
       <c r="E481" t="n">
@@ -65336,7 +65336,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_7</t>
+          <t>Mon_2576</t>
         </is>
       </c>
       <c r="E482" t="n">
@@ -65471,7 +65471,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_8</t>
+          <t>Mon_2577</t>
         </is>
       </c>
       <c r="E483" t="n">
@@ -65606,7 +65606,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_9</t>
+          <t>Mon_2578</t>
         </is>
       </c>
       <c r="E484" t="n">
@@ -65741,7 +65741,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2579</t>
         </is>
       </c>
       <c r="E485" t="n">
@@ -65876,7 +65876,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2580</t>
         </is>
       </c>
       <c r="E486" t="n">
@@ -66011,7 +66011,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2581</t>
         </is>
       </c>
       <c r="E487" t="n">
@@ -66146,7 +66146,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2582</t>
         </is>
       </c>
       <c r="E488" t="n">
@@ -66281,7 +66281,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2583</t>
         </is>
       </c>
       <c r="E489" t="n">
@@ -66416,7 +66416,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2584</t>
         </is>
       </c>
       <c r="E490" t="n">
@@ -66551,7 +66551,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2585</t>
         </is>
       </c>
       <c r="E491" t="n">
@@ -66686,7 +66686,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2586</t>
         </is>
       </c>
       <c r="E492" t="n">
@@ -66821,7 +66821,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2587</t>
         </is>
       </c>
       <c r="E493" t="n">
@@ -66956,7 +66956,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2588</t>
         </is>
       </c>
       <c r="E494" t="n">
@@ -67091,7 +67091,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2589</t>
         </is>
       </c>
       <c r="E495" t="n">
@@ -67226,7 +67226,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2590</t>
         </is>
       </c>
       <c r="E496" t="n">
@@ -67361,7 +67361,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_6</t>
+          <t>Mon_2591</t>
         </is>
       </c>
       <c r="E497" t="n">
@@ -67496,7 +67496,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_7</t>
+          <t>Mon_2592</t>
         </is>
       </c>
       <c r="E498" t="n">
@@ -67631,7 +67631,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_8</t>
+          <t>Mon_2593</t>
         </is>
       </c>
       <c r="E499" t="n">
@@ -67766,7 +67766,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_9</t>
+          <t>Mon_2594</t>
         </is>
       </c>
       <c r="E500" t="n">
@@ -67901,7 +67901,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_0</t>
+          <t>Mon_2595</t>
         </is>
       </c>
       <c r="E501" t="n">
@@ -68036,7 +68036,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_1</t>
+          <t>Mon_2596</t>
         </is>
       </c>
       <c r="E502" t="n">
@@ -68171,7 +68171,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_2</t>
+          <t>Mon_2597</t>
         </is>
       </c>
       <c r="E503" t="n">
@@ -68306,7 +68306,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_3</t>
+          <t>Mon_2598</t>
         </is>
       </c>
       <c r="E504" t="n">
@@ -68441,7 +68441,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_4</t>
+          <t>Mon_2599</t>
         </is>
       </c>
       <c r="E505" t="n">
@@ -68576,7 +68576,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Mon_RuinedSanctum_5</t>
+          <t>Mon_2600</t>
         </is>
       </c>
       <c r="E506" t="n">

--- a/Assets/@Resources/Data/Excel/CreatureData.xlsx
+++ b/Assets/@Resources/Data/Excel/CreatureData.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Mon_2003</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
